--- a/source/bin/excel/desktop.xlsx
+++ b/source/bin/excel/desktop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE4A75A-FC21-4F7C-8BB7-E17F05536B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4044106B-90FF-47E9-9E9D-52ADA9674A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -22,12 +22,23 @@
     <sheet name="tour_preset_rule" sheetId="8" r:id="rId7"/>
     <sheet name="枚举说明" sheetId="3" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="522">
   <si>
     <t>sheet</t>
   </si>
@@ -1717,12 +1728,50 @@
     <t>三麻默认规则</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>下克上</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>xiakeshang</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>下克上</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>xiakeshang_mode</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/room_rule/xiakeshang.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>下克上</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Upside Down</t>
+  </si>
+  <si>
+    <t>하극상</t>
+  </si>
+  <si>
+    <t>myres2/activity_banner/interval/xiakeshang.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆襲の戦</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1851,6 +1900,14 @@
       <color rgb="FFFF0000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1999,7 +2056,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2117,6 +2174,17 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2555,7 +2623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BK79"/>
+  <dimension ref="A1:BL79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -2567,35 +2635,36 @@
     <col min="8" max="12" width="21.375" customWidth="1"/>
     <col min="13" max="21" width="16.875" customWidth="1"/>
     <col min="22" max="22" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="9" customWidth="1"/>
-    <col min="25" max="25" width="10.625" customWidth="1"/>
-    <col min="26" max="26" width="15.25" customWidth="1"/>
-    <col min="27" max="27" width="17.625" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="14.625" customWidth="1"/>
-    <col min="30" max="30" width="15.375" customWidth="1"/>
-    <col min="31" max="31" width="9" style="25"/>
-    <col min="32" max="32" width="36.875" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="28.25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.375" customWidth="1"/>
-    <col min="37" max="38" width="9.375" customWidth="1"/>
-    <col min="39" max="39" width="13.75" customWidth="1"/>
-    <col min="40" max="43" width="10.375" customWidth="1"/>
-    <col min="44" max="44" width="9.125" customWidth="1"/>
-    <col min="45" max="45" width="9" customWidth="1"/>
-    <col min="46" max="46" width="10.375" customWidth="1"/>
-    <col min="47" max="47" width="11.25" customWidth="1"/>
-    <col min="48" max="51" width="10.625" customWidth="1"/>
-    <col min="52" max="52" width="13" customWidth="1"/>
-    <col min="53" max="53" width="14.125" customWidth="1"/>
-    <col min="54" max="54" width="6.375" customWidth="1"/>
-    <col min="55" max="56" width="12.625" customWidth="1"/>
-    <col min="57" max="60" width="16.125" customWidth="1"/>
-    <col min="61" max="63" width="17.25" customWidth="1"/>
+    <col min="23" max="23" width="19.875" customWidth="1"/>
+    <col min="24" max="25" width="9" customWidth="1"/>
+    <col min="26" max="26" width="10.625" customWidth="1"/>
+    <col min="27" max="27" width="15.25" customWidth="1"/>
+    <col min="28" max="28" width="17.625" customWidth="1"/>
+    <col min="29" max="29" width="14" customWidth="1"/>
+    <col min="30" max="30" width="14.625" customWidth="1"/>
+    <col min="31" max="31" width="15.375" customWidth="1"/>
+    <col min="32" max="32" width="9.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="36.875" style="25" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.375" customWidth="1"/>
+    <col min="38" max="39" width="9.375" customWidth="1"/>
+    <col min="40" max="40" width="13.75" customWidth="1"/>
+    <col min="41" max="44" width="10.375" customWidth="1"/>
+    <col min="45" max="45" width="9.125" customWidth="1"/>
+    <col min="46" max="46" width="9" customWidth="1"/>
+    <col min="47" max="47" width="10.375" customWidth="1"/>
+    <col min="48" max="48" width="11.25" customWidth="1"/>
+    <col min="49" max="52" width="10.625" customWidth="1"/>
+    <col min="53" max="53" width="13" customWidth="1"/>
+    <col min="54" max="54" width="14.125" customWidth="1"/>
+    <col min="55" max="55" width="6.375" customWidth="1"/>
+    <col min="56" max="57" width="12.625" customWidth="1"/>
+    <col min="58" max="61" width="16.125" customWidth="1"/>
+    <col min="62" max="64" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -2662,131 +2731,134 @@
       <c r="V1" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="X1" t="s">
         <v>34</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>35</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>36</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>37</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>38</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>39</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>40</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="AE1" s="22" t="s">
+      <c r="AF1" s="22" t="s">
         <v>311</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>312</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>313</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>314</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>42</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>43</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>44</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>45</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>46</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>47</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>49</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>50</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>51</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>52</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>53</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>54</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>55</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>56</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>57</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>58</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>59</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>60</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>61</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>62</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>63</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>64</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>65</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>66</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>67</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>68</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -2853,102 +2925,105 @@
       <c r="V2" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="X2" t="s">
         <v>87</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>89</v>
       </c>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="22" t="s">
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="AF2" s="22" t="s">
+      <c r="AG2" s="22" t="s">
         <v>490</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>320</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>90</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>91</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>92</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>93</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>94</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>95</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>96</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>97</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>98</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>99</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>100</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>101</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>102</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>103</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>104</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>105</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>106</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>107</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>108</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>109</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>110</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>111</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>112</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>113</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>115</v>
       </c>
@@ -3025,7 +3100,7 @@
         <v>116</v>
       </c>
       <c r="Z3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AA3" t="s">
         <v>117</v>
@@ -3036,20 +3111,20 @@
       <c r="AC3" t="s">
         <v>117</v>
       </c>
-      <c r="AD3" s="10" t="s">
+      <c r="AD3" t="s">
         <v>117</v>
       </c>
-      <c r="AE3" s="24" t="s">
+      <c r="AE3" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AF3" s="24" t="s">
         <v>117</v>
       </c>
       <c r="AG3" t="s">
         <v>117</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>118</v>
+      <c r="AH3" t="s">
+        <v>117</v>
       </c>
       <c r="AK3" t="s">
         <v>118</v>
@@ -3097,24 +3172,24 @@
         <v>118</v>
       </c>
       <c r="AZ3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BA3" t="s">
         <v>116</v>
       </c>
       <c r="BB3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BC3" t="s">
         <v>118</v>
       </c>
       <c r="BD3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BE3" t="s">
         <v>116</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="BF3" t="s">
         <v>116</v>
       </c>
       <c r="BJ3" t="s">
@@ -3123,8 +3198,11 @@
       <c r="BK3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BL3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>1</v>
       </c>
@@ -3137,39 +3215,36 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="s">
         <v>119</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>120</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>121</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>122</v>
       </c>
-      <c r="AD4" s="10" t="s">
+      <c r="AE4" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
       <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
         <v>-1</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
       <c r="AM4">
         <v>0</v>
       </c>
@@ -3189,35 +3264,35 @@
         <v>0</v>
       </c>
       <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
         <v>25000</v>
       </c>
-      <c r="AT4">
+      <c r="AU4">
         <v>30000</v>
       </c>
-      <c r="AU4">
+      <c r="AV4">
         <v>25000</v>
       </c>
-      <c r="AV4">
+      <c r="AW4">
         <v>15</v>
       </c>
-      <c r="AW4">
+      <c r="AX4">
         <v>5</v>
       </c>
-      <c r="AX4">
+      <c r="AY4">
         <v>-5</v>
       </c>
-      <c r="AY4">
+      <c r="AZ4">
         <v>-15</v>
       </c>
-      <c r="AZ4">
+      <c r="BA4">
         <v>10101</v>
       </c>
-      <c r="BA4">
+      <c r="BB4">
         <v>10203</v>
       </c>
-      <c r="BB4">
-        <v>0</v>
-      </c>
       <c r="BC4">
         <v>0</v>
       </c>
@@ -3236,8 +3311,11 @@
       <c r="BH4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BI4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2</v>
       </c>
@@ -3250,51 +3328,48 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="W5">
-        <v>1</v>
-      </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="s">
         <v>119</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>120</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>121</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>122</v>
       </c>
-      <c r="AD5" s="10" t="s">
+      <c r="AE5" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
       <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
         <v>-1</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
       <c r="AM5">
         <v>0</v>
       </c>
       <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
         <v>10</v>
       </c>
-      <c r="AO5">
+      <c r="AP5">
         <v>5</v>
       </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
       <c r="AQ5">
         <v>0</v>
       </c>
@@ -3302,35 +3377,35 @@
         <v>0</v>
       </c>
       <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
         <v>25000</v>
       </c>
-      <c r="AT5">
+      <c r="AU5">
         <v>30000</v>
       </c>
-      <c r="AU5">
+      <c r="AV5">
         <v>25000</v>
       </c>
-      <c r="AV5">
+      <c r="AW5">
         <v>15</v>
       </c>
-      <c r="AW5">
+      <c r="AX5">
         <v>5</v>
       </c>
-      <c r="AX5">
+      <c r="AY5">
         <v>-5</v>
       </c>
-      <c r="AY5">
+      <c r="AZ5">
         <v>-15</v>
       </c>
-      <c r="AZ5">
+      <c r="BA5">
         <v>10101</v>
       </c>
-      <c r="BA5">
+      <c r="BB5">
         <v>10203</v>
       </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
       <c r="BC5">
         <v>0</v>
       </c>
@@ -3349,8 +3424,11 @@
       <c r="BH5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BI5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>3</v>
       </c>
@@ -3363,51 +3441,48 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
       <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
         <v>2</v>
       </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="s">
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="s">
         <v>119</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>120</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>121</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>122</v>
       </c>
-      <c r="AD6" s="10" t="s">
+      <c r="AE6" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
       <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
         <v>-1</v>
       </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
       <c r="AM6">
         <v>0</v>
       </c>
       <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
         <v>20</v>
       </c>
-      <c r="AO6">
+      <c r="AP6">
         <v>10</v>
       </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
       <c r="AQ6">
         <v>0</v>
       </c>
@@ -3415,35 +3490,35 @@
         <v>0</v>
       </c>
       <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
         <v>25000</v>
       </c>
-      <c r="AT6">
+      <c r="AU6">
         <v>30000</v>
       </c>
-      <c r="AU6">
+      <c r="AV6">
         <v>25000</v>
       </c>
-      <c r="AV6">
+      <c r="AW6">
         <v>15</v>
       </c>
-      <c r="AW6">
+      <c r="AX6">
         <v>5</v>
       </c>
-      <c r="AX6">
+      <c r="AY6">
         <v>-5</v>
       </c>
-      <c r="AY6">
+      <c r="AZ6">
         <v>-15</v>
       </c>
-      <c r="AZ6">
+      <c r="BA6">
         <v>10101</v>
       </c>
-      <c r="BA6">
+      <c r="BB6">
         <v>10203</v>
       </c>
-      <c r="BB6">
-        <v>0</v>
-      </c>
       <c r="BC6">
         <v>0</v>
       </c>
@@ -3462,8 +3537,11 @@
       <c r="BH6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BI6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>4</v>
       </c>
@@ -3476,39 +3554,36 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>2</v>
       </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
       <c r="Y7">
         <v>0</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="s">
         <v>124</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>125</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>126</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>127</v>
       </c>
-      <c r="AD7" s="10" t="s">
+      <c r="AE7" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="AJ7">
+      <c r="AK7">
         <v>2500</v>
       </c>
-      <c r="AK7">
+      <c r="AL7">
         <v>-1</v>
       </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
       <c r="AM7">
         <v>0</v>
       </c>
@@ -3528,35 +3603,35 @@
         <v>0</v>
       </c>
       <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
         <v>25000</v>
       </c>
-      <c r="AT7">
+      <c r="AU7">
         <v>30000</v>
       </c>
-      <c r="AU7">
+      <c r="AV7">
         <v>25000</v>
       </c>
-      <c r="AV7">
+      <c r="AW7">
         <v>15</v>
       </c>
-      <c r="AW7">
+      <c r="AX7">
         <v>5</v>
       </c>
-      <c r="AX7">
+      <c r="AY7">
         <v>-5</v>
       </c>
-      <c r="AY7">
+      <c r="AZ7">
         <v>-15</v>
       </c>
-      <c r="AZ7">
+      <c r="BA7">
         <v>10201</v>
       </c>
-      <c r="BA7">
+      <c r="BB7">
         <v>10303</v>
       </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
       <c r="BC7">
         <v>0</v>
       </c>
@@ -3575,8 +3650,11 @@
       <c r="BH7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BI7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>5</v>
       </c>
@@ -3589,51 +3667,48 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>2</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
       <c r="Y8">
         <v>1</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="s">
         <v>124</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>125</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AC8" t="s">
         <v>126</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>127</v>
       </c>
-      <c r="AD8" s="10" t="s">
+      <c r="AE8" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="AJ8">
+      <c r="AK8">
         <v>2500</v>
       </c>
-      <c r="AK8">
+      <c r="AL8">
         <v>-1</v>
       </c>
-      <c r="AL8">
+      <c r="AM8">
         <v>2500</v>
       </c>
-      <c r="AM8">
+      <c r="AN8">
         <v>50</v>
       </c>
-      <c r="AN8">
+      <c r="AO8">
         <v>20</v>
       </c>
-      <c r="AO8">
+      <c r="AP8">
         <v>10</v>
       </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
       <c r="AQ8">
         <v>0</v>
       </c>
@@ -3641,55 +3716,58 @@
         <v>0</v>
       </c>
       <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
         <v>25000</v>
       </c>
-      <c r="AT8">
+      <c r="AU8">
         <v>30000</v>
       </c>
-      <c r="AU8">
+      <c r="AV8">
         <v>25000</v>
       </c>
-      <c r="AV8">
+      <c r="AW8">
         <v>15</v>
       </c>
-      <c r="AW8">
+      <c r="AX8">
         <v>5</v>
       </c>
-      <c r="AX8">
+      <c r="AY8">
         <v>-5</v>
       </c>
-      <c r="AY8">
+      <c r="AZ8">
         <v>-15</v>
       </c>
-      <c r="AZ8">
+      <c r="BA8">
         <v>10201</v>
       </c>
-      <c r="BA8">
+      <c r="BB8">
         <v>10303</v>
       </c>
-      <c r="BB8">
+      <c r="BC8">
         <v>500</v>
       </c>
-      <c r="BC8">
+      <c r="BD8">
         <v>40</v>
       </c>
-      <c r="BD8">
-        <v>1</v>
-      </c>
       <c r="BE8">
+        <v>1</v>
+      </c>
+      <c r="BF8">
         <v>260</v>
       </c>
-      <c r="BF8">
+      <c r="BG8">
         <v>130</v>
       </c>
-      <c r="BG8">
+      <c r="BH8">
         <v>95</v>
       </c>
-      <c r="BH8">
+      <c r="BI8">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>6</v>
       </c>
@@ -3702,51 +3780,48 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="W9">
-        <v>2</v>
-      </c>
       <c r="X9">
         <v>2</v>
       </c>
       <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="s">
         <v>124</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>125</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AC9" t="s">
         <v>126</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>127</v>
       </c>
-      <c r="AD9" s="10" t="s">
+      <c r="AE9" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="AJ9">
+      <c r="AK9">
         <v>3500</v>
       </c>
-      <c r="AK9">
+      <c r="AL9">
         <v>-1</v>
       </c>
-      <c r="AL9">
+      <c r="AM9">
         <v>3500</v>
       </c>
-      <c r="AM9">
+      <c r="AN9">
         <v>70</v>
       </c>
-      <c r="AN9">
+      <c r="AO9">
         <v>40</v>
       </c>
-      <c r="AO9">
+      <c r="AP9">
         <v>20</v>
       </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
       <c r="AQ9">
         <v>0</v>
       </c>
@@ -3754,55 +3829,58 @@
         <v>0</v>
       </c>
       <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
         <v>25000</v>
       </c>
-      <c r="AT9">
+      <c r="AU9">
         <v>30000</v>
       </c>
-      <c r="AU9">
+      <c r="AV9">
         <v>25000</v>
       </c>
-      <c r="AV9">
+      <c r="AW9">
         <v>15</v>
       </c>
-      <c r="AW9">
+      <c r="AX9">
         <v>5</v>
       </c>
-      <c r="AX9">
+      <c r="AY9">
         <v>-5</v>
       </c>
-      <c r="AY9">
+      <c r="AZ9">
         <v>-15</v>
       </c>
-      <c r="AZ9">
+      <c r="BA9">
         <v>10201</v>
       </c>
-      <c r="BA9">
+      <c r="BB9">
         <v>10303</v>
       </c>
-      <c r="BB9">
+      <c r="BC9">
         <v>700</v>
       </c>
-      <c r="BC9">
+      <c r="BD9">
         <v>60</v>
       </c>
-      <c r="BD9">
-        <v>1</v>
-      </c>
       <c r="BE9">
+        <v>1</v>
+      </c>
+      <c r="BF9">
         <v>360</v>
       </c>
-      <c r="BF9">
+      <c r="BG9">
         <v>180</v>
       </c>
-      <c r="BG9">
+      <c r="BH9">
         <v>130</v>
       </c>
-      <c r="BH9">
+      <c r="BI9">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>7</v>
       </c>
@@ -3815,39 +3893,36 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>3</v>
       </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
       <c r="Y10">
         <v>0</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="s">
         <v>129</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB10" t="s">
         <v>130</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AC10" t="s">
         <v>131</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AD10" t="s">
         <v>132</v>
       </c>
-      <c r="AD10" s="10" t="s">
+      <c r="AE10" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AJ10">
+      <c r="AK10">
         <v>5000</v>
       </c>
-      <c r="AK10">
+      <c r="AL10">
         <v>-1</v>
       </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
       <c r="AM10">
         <v>0</v>
       </c>
@@ -3867,35 +3942,35 @@
         <v>0</v>
       </c>
       <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
         <v>25000</v>
       </c>
-      <c r="AT10">
+      <c r="AU10">
         <v>30000</v>
       </c>
-      <c r="AU10">
+      <c r="AV10">
         <v>25000</v>
       </c>
-      <c r="AV10">
+      <c r="AW10">
         <v>15</v>
       </c>
-      <c r="AW10">
+      <c r="AX10">
         <v>5</v>
       </c>
-      <c r="AX10">
+      <c r="AY10">
         <v>-5</v>
       </c>
-      <c r="AY10">
+      <c r="AZ10">
         <v>-15</v>
       </c>
-      <c r="AZ10">
+      <c r="BA10">
         <v>10301</v>
       </c>
-      <c r="BA10">
+      <c r="BB10">
         <v>10403</v>
       </c>
-      <c r="BB10">
-        <v>0</v>
-      </c>
       <c r="BC10">
         <v>0</v>
       </c>
@@ -3914,8 +3989,11 @@
       <c r="BH10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BI10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>8</v>
       </c>
@@ -3928,51 +4006,48 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>3</v>
       </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
       <c r="Y11">
         <v>1</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="s">
         <v>129</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB11" t="s">
         <v>130</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AC11" t="s">
         <v>131</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AD11" t="s">
         <v>132</v>
       </c>
-      <c r="AD11" s="10" t="s">
+      <c r="AE11" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AJ11">
+      <c r="AK11">
         <v>5000</v>
       </c>
-      <c r="AK11">
+      <c r="AL11">
         <v>-1</v>
       </c>
-      <c r="AL11">
+      <c r="AM11">
         <v>5000</v>
       </c>
-      <c r="AM11">
+      <c r="AN11">
         <v>100</v>
       </c>
-      <c r="AN11">
+      <c r="AO11">
         <v>40</v>
       </c>
-      <c r="AO11">
+      <c r="AP11">
         <v>20</v>
       </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
       <c r="AQ11">
         <v>0</v>
       </c>
@@ -3980,55 +4055,58 @@
         <v>0</v>
       </c>
       <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
         <v>25000</v>
       </c>
-      <c r="AT11">
+      <c r="AU11">
         <v>30000</v>
       </c>
-      <c r="AU11">
+      <c r="AV11">
         <v>25000</v>
       </c>
-      <c r="AV11">
+      <c r="AW11">
         <v>15</v>
       </c>
-      <c r="AW11">
+      <c r="AX11">
         <v>5</v>
       </c>
-      <c r="AX11">
+      <c r="AY11">
         <v>-5</v>
       </c>
-      <c r="AY11">
+      <c r="AZ11">
         <v>-15</v>
       </c>
-      <c r="AZ11">
+      <c r="BA11">
         <v>10301</v>
       </c>
-      <c r="BA11">
+      <c r="BB11">
         <v>10403</v>
       </c>
-      <c r="BB11">
+      <c r="BC11">
         <v>1000</v>
       </c>
-      <c r="BC11">
+      <c r="BD11">
         <v>40</v>
       </c>
-      <c r="BD11">
+      <c r="BE11">
         <v>2</v>
       </c>
-      <c r="BE11">
+      <c r="BF11">
         <v>260</v>
       </c>
-      <c r="BF11">
+      <c r="BG11">
         <v>130</v>
       </c>
-      <c r="BG11">
+      <c r="BH11">
         <v>95</v>
       </c>
-      <c r="BH11">
+      <c r="BI11">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>9</v>
       </c>
@@ -4041,51 +4119,48 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>3</v>
       </c>
-      <c r="X12">
+      <c r="Y12">
         <v>2</v>
       </c>
-      <c r="Y12">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="s">
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="s">
         <v>129</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>130</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
         <v>131</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AD12" t="s">
         <v>132</v>
       </c>
-      <c r="AD12" s="10" t="s">
+      <c r="AE12" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AJ12">
+      <c r="AK12">
         <v>7000</v>
       </c>
-      <c r="AK12">
+      <c r="AL12">
         <v>-1</v>
       </c>
-      <c r="AL12">
+      <c r="AM12">
         <v>7000</v>
       </c>
-      <c r="AM12">
+      <c r="AN12">
         <v>140</v>
       </c>
-      <c r="AN12">
+      <c r="AO12">
         <v>80</v>
       </c>
-      <c r="AO12">
+      <c r="AP12">
         <v>40</v>
       </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
       <c r="AQ12">
         <v>0</v>
       </c>
@@ -4093,55 +4168,58 @@
         <v>0</v>
       </c>
       <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
         <v>25000</v>
       </c>
-      <c r="AT12">
+      <c r="AU12">
         <v>30000</v>
       </c>
-      <c r="AU12">
+      <c r="AV12">
         <v>25000</v>
       </c>
-      <c r="AV12">
+      <c r="AW12">
         <v>15</v>
       </c>
-      <c r="AW12">
+      <c r="AX12">
         <v>5</v>
       </c>
-      <c r="AX12">
+      <c r="AY12">
         <v>-5</v>
       </c>
-      <c r="AY12">
+      <c r="AZ12">
         <v>-15</v>
       </c>
-      <c r="AZ12">
+      <c r="BA12">
         <v>10301</v>
       </c>
-      <c r="BA12">
+      <c r="BB12">
         <v>10403</v>
       </c>
-      <c r="BB12">
+      <c r="BC12">
         <v>1400</v>
       </c>
-      <c r="BC12">
+      <c r="BD12">
         <v>60</v>
       </c>
-      <c r="BD12">
+      <c r="BE12">
         <v>2</v>
       </c>
-      <c r="BE12">
+      <c r="BF12">
         <v>360</v>
       </c>
-      <c r="BF12">
+      <c r="BG12">
         <v>180</v>
       </c>
-      <c r="BG12">
+      <c r="BH12">
         <v>130</v>
       </c>
-      <c r="BH12">
+      <c r="BI12">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>10</v>
       </c>
@@ -4154,39 +4232,36 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>4</v>
       </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
       <c r="Y13">
         <v>0</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="s">
         <v>134</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>135</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
         <v>136</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AD13" t="s">
         <v>137</v>
       </c>
-      <c r="AD13" s="10" t="s">
+      <c r="AE13" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AJ13">
+      <c r="AK13">
         <v>10000</v>
       </c>
-      <c r="AK13">
+      <c r="AL13">
         <v>-1</v>
       </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
       <c r="AM13">
         <v>0</v>
       </c>
@@ -4206,35 +4281,35 @@
         <v>0</v>
       </c>
       <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
         <v>25000</v>
       </c>
-      <c r="AT13">
+      <c r="AU13">
         <v>30000</v>
       </c>
-      <c r="AU13">
+      <c r="AV13">
         <v>25000</v>
       </c>
-      <c r="AV13">
+      <c r="AW13">
         <v>15</v>
       </c>
-      <c r="AW13">
+      <c r="AX13">
         <v>5</v>
       </c>
-      <c r="AX13">
+      <c r="AY13">
         <v>-5</v>
       </c>
-      <c r="AY13">
+      <c r="AZ13">
         <v>-15</v>
       </c>
-      <c r="AZ13">
+      <c r="BA13">
         <v>10401</v>
       </c>
-      <c r="BA13">
+      <c r="BB13">
         <v>10503</v>
       </c>
-      <c r="BB13">
-        <v>0</v>
-      </c>
       <c r="BC13">
         <v>0</v>
       </c>
@@ -4253,8 +4328,11 @@
       <c r="BH13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BI13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>11</v>
       </c>
@@ -4267,51 +4345,48 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>4</v>
       </c>
-      <c r="X14">
-        <v>1</v>
-      </c>
       <c r="Y14">
         <v>1</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="s">
         <v>134</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AB14" t="s">
         <v>135</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
         <v>136</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AD14" t="s">
         <v>137</v>
       </c>
-      <c r="AD14" s="10" t="s">
+      <c r="AE14" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AJ14">
+      <c r="AK14">
         <v>10000</v>
       </c>
-      <c r="AK14">
+      <c r="AL14">
         <v>-1</v>
       </c>
-      <c r="AL14">
+      <c r="AM14">
         <v>10000</v>
       </c>
-      <c r="AM14">
+      <c r="AN14">
         <v>200</v>
       </c>
-      <c r="AN14">
+      <c r="AO14">
         <v>55</v>
       </c>
-      <c r="AO14">
+      <c r="AP14">
         <v>30</v>
       </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
       <c r="AQ14">
         <v>0</v>
       </c>
@@ -4319,55 +4394,58 @@
         <v>0</v>
       </c>
       <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
         <v>25000</v>
       </c>
-      <c r="AT14">
+      <c r="AU14">
         <v>30000</v>
       </c>
-      <c r="AU14">
+      <c r="AV14">
         <v>25000</v>
       </c>
-      <c r="AV14">
+      <c r="AW14">
         <v>15</v>
       </c>
-      <c r="AW14">
+      <c r="AX14">
         <v>5</v>
       </c>
-      <c r="AX14">
+      <c r="AY14">
         <v>-5</v>
       </c>
-      <c r="AY14">
+      <c r="AZ14">
         <v>-15</v>
       </c>
-      <c r="AZ14">
+      <c r="BA14">
         <v>10401</v>
       </c>
-      <c r="BA14">
+      <c r="BB14">
         <v>10503</v>
       </c>
-      <c r="BB14">
+      <c r="BC14">
         <v>2000</v>
       </c>
-      <c r="BC14">
+      <c r="BD14">
         <v>40</v>
       </c>
-      <c r="BD14">
+      <c r="BE14">
         <v>3</v>
       </c>
-      <c r="BE14">
+      <c r="BF14">
         <v>260</v>
       </c>
-      <c r="BF14">
+      <c r="BG14">
         <v>130</v>
       </c>
-      <c r="BG14">
+      <c r="BH14">
         <v>95</v>
       </c>
-      <c r="BH14">
+      <c r="BI14">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>12</v>
       </c>
@@ -4380,51 +4458,48 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>4</v>
       </c>
-      <c r="X15">
+      <c r="Y15">
         <v>2</v>
       </c>
-      <c r="Y15">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="s">
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="s">
         <v>134</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>135</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AC15" t="s">
         <v>136</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AD15" t="s">
         <v>137</v>
       </c>
-      <c r="AD15" s="10" t="s">
+      <c r="AE15" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AJ15">
+      <c r="AK15">
         <v>14000</v>
       </c>
-      <c r="AK15">
+      <c r="AL15">
         <v>-1</v>
       </c>
-      <c r="AL15">
+      <c r="AM15">
         <v>14000</v>
       </c>
-      <c r="AM15">
+      <c r="AN15">
         <v>280</v>
       </c>
-      <c r="AN15">
+      <c r="AO15">
         <v>110</v>
       </c>
-      <c r="AO15">
+      <c r="AP15">
         <v>55</v>
       </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
       <c r="AQ15">
         <v>0</v>
       </c>
@@ -4432,55 +4507,58 @@
         <v>0</v>
       </c>
       <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
         <v>25000</v>
       </c>
-      <c r="AT15">
+      <c r="AU15">
         <v>30000</v>
       </c>
-      <c r="AU15">
+      <c r="AV15">
         <v>25000</v>
       </c>
-      <c r="AV15">
+      <c r="AW15">
         <v>15</v>
       </c>
-      <c r="AW15">
+      <c r="AX15">
         <v>5</v>
       </c>
-      <c r="AX15">
+      <c r="AY15">
         <v>-5</v>
       </c>
-      <c r="AY15">
+      <c r="AZ15">
         <v>-15</v>
       </c>
-      <c r="AZ15">
+      <c r="BA15">
         <v>10401</v>
       </c>
-      <c r="BA15">
+      <c r="BB15">
         <v>10503</v>
       </c>
-      <c r="BB15">
+      <c r="BC15">
         <v>2800</v>
       </c>
-      <c r="BC15">
+      <c r="BD15">
         <v>60</v>
       </c>
-      <c r="BD15">
+      <c r="BE15">
         <v>3</v>
       </c>
-      <c r="BE15">
+      <c r="BF15">
         <v>360</v>
       </c>
-      <c r="BF15">
+      <c r="BG15">
         <v>180</v>
       </c>
-      <c r="BG15">
+      <c r="BH15">
         <v>130</v>
       </c>
-      <c r="BH15">
+      <c r="BI15">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>13</v>
       </c>
@@ -4499,39 +4577,36 @@
       <c r="G16">
         <v>1</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <v>5</v>
       </c>
-      <c r="X16">
-        <v>1</v>
-      </c>
       <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="s">
         <v>139</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>140</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AC16" t="s">
         <v>141</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AD16" t="s">
         <v>142</v>
       </c>
-      <c r="AD16" s="10" t="s">
+      <c r="AE16" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
       <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
         <v>-1</v>
       </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
       <c r="AM16">
         <v>0</v>
       </c>
@@ -4551,29 +4626,29 @@
         <v>0</v>
       </c>
       <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
         <v>25000</v>
       </c>
-      <c r="AT16">
+      <c r="AU16">
         <v>30000</v>
       </c>
-      <c r="AU16">
+      <c r="AV16">
         <v>25000</v>
       </c>
-      <c r="AV16">
+      <c r="AW16">
         <v>15</v>
       </c>
-      <c r="AW16">
+      <c r="AX16">
         <v>5</v>
       </c>
-      <c r="AX16">
+      <c r="AY16">
         <v>-5</v>
       </c>
-      <c r="AY16">
+      <c r="AZ16">
         <v>-15</v>
       </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
       <c r="BA16">
         <v>0</v>
       </c>
@@ -4598,8 +4673,11 @@
       <c r="BH16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>14</v>
       </c>
@@ -4618,39 +4696,36 @@
       <c r="G17">
         <v>1</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <v>5</v>
       </c>
-      <c r="X17">
+      <c r="Y17">
         <v>2</v>
       </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="s">
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="s">
         <v>139</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>140</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AC17" t="s">
         <v>141</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AD17" t="s">
         <v>142</v>
       </c>
-      <c r="AD17" s="10" t="s">
+      <c r="AE17" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
       <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
         <v>-1</v>
       </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
       <c r="AM17">
         <v>0</v>
       </c>
@@ -4670,29 +4745,29 @@
         <v>0</v>
       </c>
       <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
         <v>25000</v>
       </c>
-      <c r="AT17">
+      <c r="AU17">
         <v>30000</v>
       </c>
-      <c r="AU17">
+      <c r="AV17">
         <v>25000</v>
       </c>
-      <c r="AV17">
+      <c r="AW17">
         <v>15</v>
       </c>
-      <c r="AW17">
+      <c r="AX17">
         <v>5</v>
       </c>
-      <c r="AX17">
+      <c r="AY17">
         <v>-5</v>
       </c>
-      <c r="AY17">
+      <c r="AZ17">
         <v>-15</v>
       </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
       <c r="BA17">
         <v>0</v>
       </c>
@@ -4717,8 +4792,11 @@
       <c r="BH17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>15</v>
       </c>
@@ -4731,51 +4809,48 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>6</v>
       </c>
-      <c r="X18">
-        <v>1</v>
-      </c>
       <c r="Y18">
         <v>1</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="s">
         <v>144</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>145</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AC18" t="s">
         <v>146</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AD18" t="s">
         <v>147</v>
       </c>
-      <c r="AD18" s="10" t="s">
+      <c r="AE18" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="AJ18">
+      <c r="AK18">
         <v>10000</v>
       </c>
-      <c r="AK18">
+      <c r="AL18">
         <v>-1</v>
       </c>
-      <c r="AL18">
+      <c r="AM18">
         <v>10000</v>
       </c>
-      <c r="AM18">
+      <c r="AN18">
         <v>200</v>
       </c>
-      <c r="AN18">
+      <c r="AO18">
         <v>60</v>
       </c>
-      <c r="AO18">
+      <c r="AP18">
         <v>30</v>
       </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
       <c r="AQ18">
         <v>0</v>
       </c>
@@ -4783,55 +4858,58 @@
         <v>0</v>
       </c>
       <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
         <v>25000</v>
       </c>
-      <c r="AT18">
+      <c r="AU18">
         <v>30000</v>
       </c>
-      <c r="AU18">
+      <c r="AV18">
         <v>25000</v>
       </c>
-      <c r="AV18">
+      <c r="AW18">
         <v>15</v>
       </c>
-      <c r="AW18">
+      <c r="AX18">
         <v>5</v>
       </c>
-      <c r="AX18">
+      <c r="AY18">
         <v>-5</v>
       </c>
-      <c r="AY18">
+      <c r="AZ18">
         <v>-15</v>
       </c>
-      <c r="AZ18">
+      <c r="BA18">
         <v>10501</v>
       </c>
-      <c r="BA18">
+      <c r="BB18">
         <v>10720</v>
       </c>
-      <c r="BB18">
+      <c r="BC18">
         <v>2000</v>
       </c>
-      <c r="BC18">
+      <c r="BD18">
         <v>40</v>
       </c>
-      <c r="BD18">
+      <c r="BE18">
         <v>4</v>
       </c>
-      <c r="BE18">
+      <c r="BF18">
         <v>260</v>
       </c>
-      <c r="BF18">
+      <c r="BG18">
         <v>130</v>
       </c>
-      <c r="BG18">
+      <c r="BH18">
         <v>95</v>
       </c>
-      <c r="BH18">
+      <c r="BI18">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>16</v>
       </c>
@@ -4844,51 +4922,48 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <v>6</v>
       </c>
-      <c r="X19">
+      <c r="Y19">
         <v>2</v>
       </c>
-      <c r="Y19">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="s">
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="s">
         <v>144</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB19" t="s">
         <v>145</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AC19" t="s">
         <v>146</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AD19" t="s">
         <v>147</v>
       </c>
-      <c r="AD19" s="10" t="s">
+      <c r="AE19" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="AJ19">
+      <c r="AK19">
         <v>14000</v>
       </c>
-      <c r="AK19">
+      <c r="AL19">
         <v>-1</v>
       </c>
-      <c r="AL19">
+      <c r="AM19">
         <v>14000</v>
       </c>
-      <c r="AM19">
+      <c r="AN19">
         <v>280</v>
       </c>
-      <c r="AN19">
+      <c r="AO19">
         <v>120</v>
       </c>
-      <c r="AO19">
+      <c r="AP19">
         <v>60</v>
       </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
       <c r="AQ19">
         <v>0</v>
       </c>
@@ -4896,55 +4971,58 @@
         <v>0</v>
       </c>
       <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
         <v>25000</v>
       </c>
-      <c r="AT19">
+      <c r="AU19">
         <v>30000</v>
       </c>
-      <c r="AU19">
+      <c r="AV19">
         <v>25000</v>
       </c>
-      <c r="AV19">
+      <c r="AW19">
         <v>15</v>
       </c>
-      <c r="AW19">
+      <c r="AX19">
         <v>5</v>
       </c>
-      <c r="AX19">
+      <c r="AY19">
         <v>-5</v>
       </c>
-      <c r="AY19">
+      <c r="AZ19">
         <v>-15</v>
       </c>
-      <c r="AZ19">
+      <c r="BA19">
         <v>10501</v>
       </c>
-      <c r="BA19">
+      <c r="BB19">
         <v>10720</v>
       </c>
-      <c r="BB19">
+      <c r="BC19">
         <v>2800</v>
       </c>
-      <c r="BC19">
+      <c r="BD19">
         <v>60</v>
       </c>
-      <c r="BD19">
+      <c r="BE19">
         <v>4</v>
       </c>
-      <c r="BE19">
+      <c r="BF19">
         <v>360</v>
       </c>
-      <c r="BF19">
+      <c r="BG19">
         <v>180</v>
       </c>
-      <c r="BG19">
+      <c r="BH19">
         <v>130</v>
       </c>
-      <c r="BH19">
+      <c r="BI19">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>17</v>
       </c>
@@ -4957,48 +5035,45 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="W20">
-        <v>1</v>
-      </c>
       <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
         <v>11</v>
       </c>
-      <c r="Y20">
-        <v>1</v>
-      </c>
-      <c r="Z20" t="s">
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="s">
         <v>119</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>120</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AC20" t="s">
         <v>121</v>
       </c>
-      <c r="AC20" t="s">
+      <c r="AD20" t="s">
         <v>122</v>
       </c>
-      <c r="AD20" s="10" t="s">
+      <c r="AE20" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
       <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
         <v>-1</v>
       </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
       <c r="AM20">
         <v>0</v>
       </c>
       <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
         <v>15</v>
       </c>
-      <c r="AO20">
-        <v>0</v>
-      </c>
       <c r="AP20">
         <v>0</v>
       </c>
@@ -5009,35 +5084,35 @@
         <v>0</v>
       </c>
       <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
         <v>35000</v>
       </c>
-      <c r="AT20">
+      <c r="AU20">
         <v>40000</v>
       </c>
-      <c r="AU20">
+      <c r="AV20">
         <v>35000</v>
       </c>
-      <c r="AV20">
+      <c r="AW20">
         <v>15</v>
       </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
       <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
         <v>-15</v>
       </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
       <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
         <v>20101</v>
       </c>
-      <c r="BA20">
+      <c r="BB20">
         <v>20203</v>
       </c>
-      <c r="BB20">
-        <v>0</v>
-      </c>
       <c r="BC20">
         <v>0</v>
       </c>
@@ -5056,8 +5131,11 @@
       <c r="BH20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>18</v>
       </c>
@@ -5070,48 +5148,45 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="W21">
-        <v>1</v>
-      </c>
       <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
         <v>12</v>
       </c>
-      <c r="Y21">
-        <v>1</v>
-      </c>
-      <c r="Z21" t="s">
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="s">
         <v>119</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB21" t="s">
         <v>120</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AC21" t="s">
         <v>121</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AD21" t="s">
         <v>122</v>
       </c>
-      <c r="AD21" s="10" t="s">
+      <c r="AE21" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
       <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
         <v>-1</v>
       </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
       <c r="AM21">
         <v>0</v>
       </c>
       <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
         <v>30</v>
       </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
       <c r="AP21">
         <v>0</v>
       </c>
@@ -5122,35 +5197,35 @@
         <v>0</v>
       </c>
       <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
         <v>35000</v>
       </c>
-      <c r="AT21">
+      <c r="AU21">
         <v>40000</v>
       </c>
-      <c r="AU21">
+      <c r="AV21">
         <v>35000</v>
       </c>
-      <c r="AV21">
+      <c r="AW21">
         <v>15</v>
       </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
       <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
         <v>-15</v>
       </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
       <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
         <v>20101</v>
       </c>
-      <c r="BA21">
+      <c r="BB21">
         <v>20203</v>
       </c>
-      <c r="BB21">
-        <v>0</v>
-      </c>
       <c r="BC21">
         <v>0</v>
       </c>
@@ -5169,8 +5244,11 @@
       <c r="BH21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>19</v>
       </c>
@@ -5183,48 +5261,45 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <v>2</v>
       </c>
-      <c r="X22">
+      <c r="Y22">
         <v>11</v>
       </c>
-      <c r="Y22">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="s">
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="s">
         <v>124</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="AB22" t="s">
         <v>125</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AC22" t="s">
         <v>126</v>
       </c>
-      <c r="AC22" t="s">
+      <c r="AD22" t="s">
         <v>127</v>
       </c>
-      <c r="AD22" s="10" t="s">
+      <c r="AE22" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="AJ22">
+      <c r="AK22">
         <v>2500</v>
       </c>
-      <c r="AK22">
+      <c r="AL22">
         <v>-1</v>
       </c>
-      <c r="AL22">
+      <c r="AM22">
         <v>2500</v>
       </c>
-      <c r="AM22">
+      <c r="AN22">
         <v>50</v>
       </c>
-      <c r="AN22">
+      <c r="AO22">
         <v>30</v>
       </c>
-      <c r="AO22">
-        <v>0</v>
-      </c>
       <c r="AP22">
         <v>0</v>
       </c>
@@ -5235,55 +5310,58 @@
         <v>0</v>
       </c>
       <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
         <v>35000</v>
       </c>
-      <c r="AT22">
+      <c r="AU22">
         <v>40000</v>
       </c>
-      <c r="AU22">
+      <c r="AV22">
         <v>35000</v>
       </c>
-      <c r="AV22">
+      <c r="AW22">
         <v>15</v>
       </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
       <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
         <v>-15</v>
       </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
       <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
         <v>20201</v>
       </c>
-      <c r="BA22">
+      <c r="BB22">
         <v>20303</v>
       </c>
-      <c r="BB22">
+      <c r="BC22">
         <v>500</v>
       </c>
-      <c r="BC22">
+      <c r="BD22">
         <v>25</v>
       </c>
-      <c r="BD22">
-        <v>1</v>
-      </c>
       <c r="BE22">
+        <v>1</v>
+      </c>
+      <c r="BF22">
         <v>170</v>
       </c>
-      <c r="BF22">
+      <c r="BG22">
         <v>100</v>
       </c>
-      <c r="BG22">
+      <c r="BH22">
         <v>40</v>
       </c>
-      <c r="BH22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>20</v>
       </c>
@@ -5296,48 +5374,45 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>2</v>
       </c>
-      <c r="X23">
+      <c r="Y23">
         <v>12</v>
       </c>
-      <c r="Y23">
-        <v>1</v>
-      </c>
-      <c r="Z23" t="s">
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="s">
         <v>124</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>125</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AC23" t="s">
         <v>126</v>
       </c>
-      <c r="AC23" t="s">
+      <c r="AD23" t="s">
         <v>127</v>
       </c>
-      <c r="AD23" s="10" t="s">
+      <c r="AE23" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="AJ23">
+      <c r="AK23">
         <v>3500</v>
       </c>
-      <c r="AK23">
+      <c r="AL23">
         <v>-1</v>
       </c>
-      <c r="AL23">
+      <c r="AM23">
         <v>3500</v>
       </c>
-      <c r="AM23">
+      <c r="AN23">
         <v>70</v>
       </c>
-      <c r="AN23">
+      <c r="AO23">
         <v>60</v>
       </c>
-      <c r="AO23">
-        <v>0</v>
-      </c>
       <c r="AP23">
         <v>0</v>
       </c>
@@ -5348,55 +5423,58 @@
         <v>0</v>
       </c>
       <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
         <v>35000</v>
       </c>
-      <c r="AT23">
+      <c r="AU23">
         <v>40000</v>
       </c>
-      <c r="AU23">
+      <c r="AV23">
         <v>35000</v>
       </c>
-      <c r="AV23">
+      <c r="AW23">
         <v>15</v>
       </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
       <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
         <v>-15</v>
       </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
       <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
         <v>20201</v>
       </c>
-      <c r="BA23">
+      <c r="BB23">
         <v>20303</v>
       </c>
-      <c r="BB23">
+      <c r="BC23">
         <v>700</v>
       </c>
-      <c r="BC23">
+      <c r="BD23">
         <v>40</v>
       </c>
-      <c r="BD23">
-        <v>1</v>
-      </c>
       <c r="BE23">
+        <v>1</v>
+      </c>
+      <c r="BF23">
         <v>240</v>
       </c>
-      <c r="BF23">
+      <c r="BG23">
         <v>135</v>
       </c>
-      <c r="BG23">
+      <c r="BH23">
         <v>50</v>
       </c>
-      <c r="BH23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>21</v>
       </c>
@@ -5409,48 +5487,45 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>3</v>
       </c>
-      <c r="X24">
+      <c r="Y24">
         <v>11</v>
       </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
-      <c r="Z24" t="s">
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="s">
         <v>129</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AB24" t="s">
         <v>130</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AC24" t="s">
         <v>131</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AD24" t="s">
         <v>132</v>
       </c>
-      <c r="AD24" s="10" t="s">
+      <c r="AE24" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AJ24">
+      <c r="AK24">
         <v>5000</v>
       </c>
-      <c r="AK24">
+      <c r="AL24">
         <v>-1</v>
       </c>
-      <c r="AL24">
+      <c r="AM24">
         <v>5000</v>
       </c>
-      <c r="AM24">
+      <c r="AN24">
         <v>100</v>
       </c>
-      <c r="AN24">
+      <c r="AO24">
         <v>55</v>
       </c>
-      <c r="AO24">
-        <v>0</v>
-      </c>
       <c r="AP24">
         <v>0</v>
       </c>
@@ -5461,55 +5536,58 @@
         <v>0</v>
       </c>
       <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
         <v>35000</v>
       </c>
-      <c r="AT24">
+      <c r="AU24">
         <v>40000</v>
       </c>
-      <c r="AU24">
+      <c r="AV24">
         <v>35000</v>
       </c>
-      <c r="AV24">
+      <c r="AW24">
         <v>15</v>
       </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
       <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
         <v>-15</v>
       </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
       <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
         <v>20301</v>
       </c>
-      <c r="BA24">
+      <c r="BB24">
         <v>20403</v>
       </c>
-      <c r="BB24">
+      <c r="BC24">
         <v>1000</v>
       </c>
-      <c r="BC24">
+      <c r="BD24">
         <v>25</v>
       </c>
-      <c r="BD24">
+      <c r="BE24">
         <v>2</v>
       </c>
-      <c r="BE24">
+      <c r="BF24">
         <v>170</v>
       </c>
-      <c r="BF24">
+      <c r="BG24">
         <v>100</v>
       </c>
-      <c r="BG24">
+      <c r="BH24">
         <v>40</v>
       </c>
-      <c r="BH24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>22</v>
       </c>
@@ -5522,48 +5600,45 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>3</v>
       </c>
-      <c r="X25">
+      <c r="Y25">
         <v>12</v>
       </c>
-      <c r="Y25">
-        <v>1</v>
-      </c>
-      <c r="Z25" t="s">
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="s">
         <v>129</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
         <v>130</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AC25" t="s">
         <v>131</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AD25" t="s">
         <v>132</v>
       </c>
-      <c r="AD25" s="10" t="s">
+      <c r="AE25" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AJ25">
+      <c r="AK25">
         <v>7000</v>
       </c>
-      <c r="AK25">
+      <c r="AL25">
         <v>-1</v>
       </c>
-      <c r="AL25">
+      <c r="AM25">
         <v>7000</v>
       </c>
-      <c r="AM25">
+      <c r="AN25">
         <v>140</v>
       </c>
-      <c r="AN25">
+      <c r="AO25">
         <v>105</v>
       </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
       <c r="AP25">
         <v>0</v>
       </c>
@@ -5574,55 +5649,58 @@
         <v>0</v>
       </c>
       <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
         <v>35000</v>
       </c>
-      <c r="AT25">
+      <c r="AU25">
         <v>40000</v>
       </c>
-      <c r="AU25">
+      <c r="AV25">
         <v>35000</v>
       </c>
-      <c r="AV25">
+      <c r="AW25">
         <v>15</v>
       </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
       <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
         <v>-15</v>
       </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
       <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
         <v>20301</v>
       </c>
-      <c r="BA25">
+      <c r="BB25">
         <v>20403</v>
       </c>
-      <c r="BB25">
+      <c r="BC25">
         <v>1400</v>
       </c>
-      <c r="BC25">
+      <c r="BD25">
         <v>40</v>
       </c>
-      <c r="BD25">
+      <c r="BE25">
         <v>2</v>
       </c>
-      <c r="BE25">
+      <c r="BF25">
         <v>240</v>
       </c>
-      <c r="BF25">
+      <c r="BG25">
         <v>135</v>
       </c>
-      <c r="BG25">
+      <c r="BH25">
         <v>50</v>
       </c>
-      <c r="BH25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>23</v>
       </c>
@@ -5635,48 +5713,45 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>4</v>
       </c>
-      <c r="X26">
+      <c r="Y26">
         <v>11</v>
       </c>
-      <c r="Y26">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="s">
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="s">
         <v>134</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB26" t="s">
         <v>135</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AC26" t="s">
         <v>136</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AD26" t="s">
         <v>137</v>
       </c>
-      <c r="AD26" s="10" t="s">
+      <c r="AE26" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AJ26">
+      <c r="AK26">
         <v>10000</v>
       </c>
-      <c r="AK26">
+      <c r="AL26">
         <v>-1</v>
       </c>
-      <c r="AL26">
+      <c r="AM26">
         <v>10000</v>
       </c>
-      <c r="AM26">
+      <c r="AN26">
         <v>200</v>
       </c>
-      <c r="AN26">
+      <c r="AO26">
         <v>75</v>
       </c>
-      <c r="AO26">
-        <v>0</v>
-      </c>
       <c r="AP26">
         <v>0</v>
       </c>
@@ -5687,55 +5762,58 @@
         <v>0</v>
       </c>
       <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
         <v>35000</v>
       </c>
-      <c r="AT26">
+      <c r="AU26">
         <v>40000</v>
       </c>
-      <c r="AU26">
+      <c r="AV26">
         <v>35000</v>
       </c>
-      <c r="AV26">
+      <c r="AW26">
         <v>15</v>
       </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
       <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
         <v>-15</v>
       </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
       <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
         <v>20401</v>
       </c>
-      <c r="BA26">
+      <c r="BB26">
         <v>20503</v>
       </c>
-      <c r="BB26">
+      <c r="BC26">
         <v>2000</v>
       </c>
-      <c r="BC26">
+      <c r="BD26">
         <v>25</v>
       </c>
-      <c r="BD26">
+      <c r="BE26">
         <v>3</v>
       </c>
-      <c r="BE26">
+      <c r="BF26">
         <v>170</v>
       </c>
-      <c r="BF26">
+      <c r="BG26">
         <v>100</v>
       </c>
-      <c r="BG26">
+      <c r="BH26">
         <v>40</v>
       </c>
-      <c r="BH26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>24</v>
       </c>
@@ -5748,48 +5826,45 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>4</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>12</v>
       </c>
-      <c r="Y27">
-        <v>1</v>
-      </c>
-      <c r="Z27" t="s">
+      <c r="Z27">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="s">
         <v>134</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>135</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AC27" t="s">
         <v>136</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AD27" t="s">
         <v>137</v>
       </c>
-      <c r="AD27" s="10" t="s">
+      <c r="AE27" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AJ27">
+      <c r="AK27">
         <v>14000</v>
       </c>
-      <c r="AK27">
+      <c r="AL27">
         <v>-1</v>
       </c>
-      <c r="AL27">
+      <c r="AM27">
         <v>14000</v>
       </c>
-      <c r="AM27">
+      <c r="AN27">
         <v>280</v>
       </c>
-      <c r="AN27">
+      <c r="AO27">
         <v>160</v>
       </c>
-      <c r="AO27">
-        <v>0</v>
-      </c>
       <c r="AP27">
         <v>0</v>
       </c>
@@ -5800,55 +5875,58 @@
         <v>0</v>
       </c>
       <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
         <v>35000</v>
       </c>
-      <c r="AT27">
+      <c r="AU27">
         <v>40000</v>
       </c>
-      <c r="AU27">
+      <c r="AV27">
         <v>35000</v>
       </c>
-      <c r="AV27">
+      <c r="AW27">
         <v>15</v>
       </c>
-      <c r="AW27">
-        <v>0</v>
-      </c>
       <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
         <v>-15</v>
       </c>
-      <c r="AY27">
-        <v>0</v>
-      </c>
       <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
         <v>20401</v>
       </c>
-      <c r="BA27">
+      <c r="BB27">
         <v>20503</v>
       </c>
-      <c r="BB27">
+      <c r="BC27">
         <v>2800</v>
       </c>
-      <c r="BC27">
+      <c r="BD27">
         <v>40</v>
       </c>
-      <c r="BD27">
+      <c r="BE27">
         <v>3</v>
       </c>
-      <c r="BE27">
+      <c r="BF27">
         <v>240</v>
       </c>
-      <c r="BF27">
+      <c r="BG27">
         <v>135</v>
       </c>
-      <c r="BG27">
+      <c r="BH27">
         <v>50</v>
       </c>
-      <c r="BH27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>25</v>
       </c>
@@ -5861,48 +5939,45 @@
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>6</v>
       </c>
-      <c r="X28">
+      <c r="Y28">
         <v>11</v>
       </c>
-      <c r="Y28">
-        <v>1</v>
-      </c>
-      <c r="Z28" t="s">
+      <c r="Z28">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="s">
         <v>144</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>145</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AC28" t="s">
         <v>146</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AD28" t="s">
         <v>147</v>
       </c>
-      <c r="AD28" s="10" t="s">
+      <c r="AE28" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="AJ28">
+      <c r="AK28">
         <v>10000</v>
       </c>
-      <c r="AK28">
+      <c r="AL28">
         <v>-1</v>
       </c>
-      <c r="AL28">
+      <c r="AM28">
         <v>10000</v>
       </c>
-      <c r="AM28">
+      <c r="AN28">
         <v>200</v>
       </c>
-      <c r="AN28">
+      <c r="AO28">
         <v>120</v>
       </c>
-      <c r="AO28">
-        <v>0</v>
-      </c>
       <c r="AP28">
         <v>0</v>
       </c>
@@ -5913,55 +5988,58 @@
         <v>0</v>
       </c>
       <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
         <v>35000</v>
       </c>
-      <c r="AT28">
+      <c r="AU28">
         <v>40000</v>
       </c>
-      <c r="AU28">
+      <c r="AV28">
         <v>35000</v>
       </c>
-      <c r="AV28">
+      <c r="AW28">
         <v>15</v>
       </c>
-      <c r="AW28">
-        <v>0</v>
-      </c>
       <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
         <v>-15</v>
       </c>
-      <c r="AY28">
-        <v>0</v>
-      </c>
       <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
         <v>20501</v>
       </c>
-      <c r="BA28">
+      <c r="BB28">
         <v>20720</v>
       </c>
-      <c r="BB28">
+      <c r="BC28">
         <v>2000</v>
       </c>
-      <c r="BC28">
+      <c r="BD28">
         <v>25</v>
       </c>
-      <c r="BD28">
+      <c r="BE28">
         <v>4</v>
       </c>
-      <c r="BE28">
+      <c r="BF28">
         <v>170</v>
       </c>
-      <c r="BF28">
+      <c r="BG28">
         <v>100</v>
       </c>
-      <c r="BG28">
+      <c r="BH28">
         <v>40</v>
       </c>
-      <c r="BH28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>26</v>
       </c>
@@ -5974,48 +6052,45 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <v>6</v>
       </c>
-      <c r="X29">
+      <c r="Y29">
         <v>12</v>
       </c>
-      <c r="Y29">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="s">
+      <c r="Z29">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="s">
         <v>144</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB29" t="s">
         <v>145</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AC29" t="s">
         <v>146</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AD29" t="s">
         <v>147</v>
       </c>
-      <c r="AD29" s="10" t="s">
+      <c r="AE29" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="AJ29">
+      <c r="AK29">
         <v>14000</v>
       </c>
-      <c r="AK29">
+      <c r="AL29">
         <v>-1</v>
       </c>
-      <c r="AL29">
+      <c r="AM29">
         <v>14000</v>
       </c>
-      <c r="AM29">
+      <c r="AN29">
         <v>280</v>
       </c>
-      <c r="AN29">
+      <c r="AO29">
         <v>240</v>
       </c>
-      <c r="AO29">
-        <v>0</v>
-      </c>
       <c r="AP29">
         <v>0</v>
       </c>
@@ -6026,55 +6101,58 @@
         <v>0</v>
       </c>
       <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
         <v>35000</v>
       </c>
-      <c r="AT29">
+      <c r="AU29">
         <v>40000</v>
       </c>
-      <c r="AU29">
+      <c r="AV29">
         <v>35000</v>
       </c>
-      <c r="AV29">
+      <c r="AW29">
         <v>15</v>
       </c>
-      <c r="AW29">
-        <v>0</v>
-      </c>
       <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
         <v>-15</v>
       </c>
-      <c r="AY29">
-        <v>0</v>
-      </c>
       <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
         <v>20501</v>
       </c>
-      <c r="BA29">
+      <c r="BB29">
         <v>20720</v>
       </c>
-      <c r="BB29">
+      <c r="BC29">
         <v>2800</v>
       </c>
-      <c r="BC29">
+      <c r="BD29">
         <v>40</v>
       </c>
-      <c r="BD29">
+      <c r="BE29">
         <v>4</v>
       </c>
-      <c r="BE29">
+      <c r="BF29">
         <v>240</v>
       </c>
-      <c r="BF29">
+      <c r="BG29">
         <v>135</v>
       </c>
-      <c r="BG29">
+      <c r="BH29">
         <v>50</v>
       </c>
-      <c r="BH29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>149</v>
       </c>
@@ -6090,39 +6168,36 @@
       <c r="E30">
         <v>3</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>100</v>
       </c>
-      <c r="X30">
-        <v>1</v>
-      </c>
       <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="s">
         <v>150</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>151</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AC30" t="s">
         <v>152</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AD30" t="s">
         <v>153</v>
       </c>
-      <c r="AD30" s="10" t="s">
+      <c r="AE30" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
       <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
         <v>-1</v>
       </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
       <c r="AM30">
         <v>0</v>
       </c>
@@ -6142,29 +6217,29 @@
         <v>0</v>
       </c>
       <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
         <v>25000</v>
       </c>
-      <c r="AT30">
+      <c r="AU30">
         <v>30000</v>
       </c>
-      <c r="AU30">
+      <c r="AV30">
         <v>25000</v>
       </c>
-      <c r="AV30">
+      <c r="AW30">
         <v>15</v>
       </c>
-      <c r="AW30">
+      <c r="AX30">
         <v>5</v>
       </c>
-      <c r="AX30">
+      <c r="AY30">
         <v>-5</v>
       </c>
-      <c r="AY30">
+      <c r="AZ30">
         <v>-15</v>
       </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
       <c r="BA30">
         <v>0</v>
       </c>
@@ -6189,8 +6264,11 @@
       <c r="BH30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>149</v>
       </c>
@@ -6206,39 +6284,36 @@
       <c r="E31">
         <v>3</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <v>100</v>
       </c>
-      <c r="X31">
+      <c r="Y31">
         <v>2</v>
       </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="s">
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="s">
         <v>150</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AB31" t="s">
         <v>151</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AC31" t="s">
         <v>152</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AD31" t="s">
         <v>153</v>
       </c>
-      <c r="AD31" s="10" t="s">
+      <c r="AE31" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
       <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
         <v>-1</v>
       </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
       <c r="AM31">
         <v>0</v>
       </c>
@@ -6258,29 +6333,29 @@
         <v>0</v>
       </c>
       <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
         <v>25000</v>
       </c>
-      <c r="AT31">
+      <c r="AU31">
         <v>30000</v>
       </c>
-      <c r="AU31">
+      <c r="AV31">
         <v>25000</v>
       </c>
-      <c r="AV31">
+      <c r="AW31">
         <v>15</v>
       </c>
-      <c r="AW31">
+      <c r="AX31">
         <v>5</v>
       </c>
-      <c r="AX31">
+      <c r="AY31">
         <v>-5</v>
       </c>
-      <c r="AY31">
+      <c r="AZ31">
         <v>-15</v>
       </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
       <c r="BA31">
         <v>0</v>
       </c>
@@ -6305,8 +6380,11 @@
       <c r="BH31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="BI31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>149</v>
       </c>
@@ -6322,39 +6400,36 @@
       <c r="E32">
         <v>3</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <v>100</v>
       </c>
-      <c r="X32">
+      <c r="Y32">
         <v>11</v>
       </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="s">
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="s">
         <v>150</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>151</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AC32" t="s">
         <v>152</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AD32" t="s">
         <v>153</v>
       </c>
-      <c r="AD32" s="10" t="s">
+      <c r="AE32" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
       <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
         <v>-1</v>
       </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
       <c r="AM32">
         <v>0</v>
       </c>
@@ -6374,26 +6449,26 @@
         <v>0</v>
       </c>
       <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
         <v>35000</v>
       </c>
-      <c r="AT32">
+      <c r="AU32">
         <v>40000</v>
       </c>
-      <c r="AU32">
+      <c r="AV32">
         <v>35000</v>
       </c>
-      <c r="AV32">
+      <c r="AW32">
         <v>15</v>
       </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
       <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
         <v>-15</v>
       </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
       <c r="AZ32">
         <v>0</v>
       </c>
@@ -6421,8 +6496,11 @@
       <c r="BH32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BI32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>149</v>
       </c>
@@ -6438,39 +6516,36 @@
       <c r="E33">
         <v>3</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <v>100</v>
       </c>
-      <c r="X33">
+      <c r="Y33">
         <v>12</v>
       </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="s">
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="s">
         <v>150</v>
       </c>
-      <c r="AA33" t="s">
+      <c r="AB33" t="s">
         <v>151</v>
       </c>
-      <c r="AB33" t="s">
+      <c r="AC33" t="s">
         <v>152</v>
       </c>
-      <c r="AC33" t="s">
+      <c r="AD33" t="s">
         <v>153</v>
       </c>
-      <c r="AD33" s="10" t="s">
+      <c r="AE33" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="AJ33">
-        <v>0</v>
-      </c>
       <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
         <v>-1</v>
       </c>
-      <c r="AL33">
-        <v>0</v>
-      </c>
       <c r="AM33">
         <v>0</v>
       </c>
@@ -6490,26 +6565,26 @@
         <v>0</v>
       </c>
       <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
         <v>35000</v>
       </c>
-      <c r="AT33">
+      <c r="AU33">
         <v>40000</v>
       </c>
-      <c r="AU33">
+      <c r="AV33">
         <v>35000</v>
       </c>
-      <c r="AV33">
+      <c r="AW33">
         <v>15</v>
       </c>
-      <c r="AW33">
-        <v>0</v>
-      </c>
       <c r="AX33">
+        <v>0</v>
+      </c>
+      <c r="AY33">
         <v>-15</v>
       </c>
-      <c r="AY33">
-        <v>0</v>
-      </c>
       <c r="AZ33">
         <v>0</v>
       </c>
@@ -6537,8 +6612,11 @@
       <c r="BH33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="BI33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>155</v>
       </c>
@@ -6560,54 +6638,51 @@
       <c r="H34">
         <v>1</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <v>200</v>
       </c>
-      <c r="X34">
-        <v>1</v>
-      </c>
       <c r="Y34">
         <v>1</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="Z34">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="s">
         <v>155</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AB34" t="s">
         <v>156</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AC34" t="s">
         <v>157</v>
       </c>
-      <c r="AC34" t="s">
+      <c r="AD34" t="s">
         <v>158</v>
       </c>
-      <c r="AD34" s="10" t="s">
+      <c r="AE34" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="AE34" s="26">
+      <c r="AF34" s="26">
         <v>3651</v>
       </c>
-      <c r="AF34" s="2" t="s">
+      <c r="AG34" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="AG34" s="2" t="s">
+      <c r="AH34" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="AJ34">
+      <c r="AK34">
         <v>5000</v>
       </c>
-      <c r="AK34">
+      <c r="AL34">
         <v>-1</v>
       </c>
-      <c r="AL34">
+      <c r="AM34">
         <v>5000</v>
       </c>
-      <c r="AM34">
+      <c r="AN34">
         <v>100</v>
       </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
       <c r="AO34">
         <v>0</v>
       </c>
@@ -6621,55 +6696,58 @@
         <v>0</v>
       </c>
       <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
         <v>35000</v>
       </c>
-      <c r="AT34">
+      <c r="AU34">
         <v>40000</v>
       </c>
-      <c r="AU34">
+      <c r="AV34">
         <v>35000</v>
       </c>
-      <c r="AV34">
+      <c r="AW34">
         <v>15</v>
       </c>
-      <c r="AW34">
+      <c r="AX34">
         <v>5</v>
       </c>
-      <c r="AX34">
+      <c r="AY34">
         <v>-5</v>
       </c>
-      <c r="AY34">
+      <c r="AZ34">
         <v>-15</v>
       </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
       <c r="BA34">
         <v>0</v>
       </c>
       <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
         <v>1000</v>
       </c>
-      <c r="BC34">
+      <c r="BD34">
         <v>40</v>
       </c>
-      <c r="BD34">
+      <c r="BE34">
         <v>5</v>
       </c>
-      <c r="BE34">
+      <c r="BF34">
         <v>260</v>
       </c>
-      <c r="BF34">
+      <c r="BG34">
         <v>130</v>
       </c>
-      <c r="BG34">
+      <c r="BH34">
         <v>95</v>
       </c>
-      <c r="BH34">
+      <c r="BI34">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>160</v>
       </c>
@@ -6691,45 +6769,42 @@
       <c r="I35">
         <v>1</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <v>210</v>
       </c>
-      <c r="X35">
-        <v>1</v>
-      </c>
       <c r="Y35">
         <v>1</v>
       </c>
-      <c r="Z35" t="s">
-        <v>160</v>
+      <c r="Z35">
+        <v>1</v>
       </c>
       <c r="AA35" t="s">
         <v>160</v>
       </c>
       <c r="AB35" t="s">
+        <v>160</v>
+      </c>
+      <c r="AC35" t="s">
         <v>161</v>
       </c>
-      <c r="AC35" t="s">
+      <c r="AD35" t="s">
         <v>162</v>
       </c>
-      <c r="AD35" s="10" t="s">
+      <c r="AE35" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="AJ35">
+      <c r="AK35">
         <v>5000</v>
       </c>
-      <c r="AK35">
+      <c r="AL35">
         <v>-1</v>
       </c>
-      <c r="AL35">
+      <c r="AM35">
         <v>5000</v>
       </c>
-      <c r="AM35">
+      <c r="AN35">
         <v>100</v>
       </c>
-      <c r="AN35">
-        <v>0</v>
-      </c>
       <c r="AO35">
         <v>0</v>
       </c>
@@ -6743,55 +6818,58 @@
         <v>0</v>
       </c>
       <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
         <v>25000</v>
       </c>
-      <c r="AT35">
+      <c r="AU35">
         <v>30000</v>
       </c>
-      <c r="AU35">
+      <c r="AV35">
         <v>25000</v>
       </c>
-      <c r="AV35">
+      <c r="AW35">
         <v>15</v>
       </c>
-      <c r="AW35">
+      <c r="AX35">
         <v>5</v>
       </c>
-      <c r="AX35">
+      <c r="AY35">
         <v>-5</v>
       </c>
-      <c r="AY35">
+      <c r="AZ35">
         <v>-15</v>
       </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
       <c r="BA35">
         <v>0</v>
       </c>
       <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
         <v>1000</v>
       </c>
-      <c r="BC35">
+      <c r="BD35">
         <v>40</v>
       </c>
-      <c r="BD35">
+      <c r="BE35">
         <v>5</v>
       </c>
-      <c r="BE35">
+      <c r="BF35">
         <v>260</v>
       </c>
-      <c r="BF35">
+      <c r="BG35">
         <v>130</v>
       </c>
-      <c r="BG35">
+      <c r="BH35">
         <v>95</v>
       </c>
-      <c r="BH35">
+      <c r="BI35">
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>164</v>
       </c>
@@ -6816,57 +6894,54 @@
       <c r="J36">
         <v>1</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <v>220</v>
       </c>
-      <c r="X36">
-        <v>1</v>
-      </c>
       <c r="Y36">
         <v>1</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="Z36">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="s">
         <v>164</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AB36" t="s">
         <v>165</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AC36" t="s">
         <v>166</v>
       </c>
-      <c r="AC36" t="s">
+      <c r="AD36" t="s">
         <v>167</v>
       </c>
-      <c r="AD36" s="10" t="s">
+      <c r="AE36" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="AE36" s="35">
+      <c r="AF36" s="35">
         <v>20422</v>
       </c>
-      <c r="AF36" s="2" t="s">
+      <c r="AG36" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="AG36" s="2" t="s">
+      <c r="AH36" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="AH36" s="2" t="s">
+      <c r="AI36" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="AJ36">
+      <c r="AK36">
         <v>5000</v>
       </c>
-      <c r="AK36">
+      <c r="AL36">
         <v>-1</v>
       </c>
-      <c r="AL36">
+      <c r="AM36">
         <v>5000</v>
       </c>
-      <c r="AM36">
+      <c r="AN36">
         <v>100</v>
       </c>
-      <c r="AN36">
-        <v>0</v>
-      </c>
       <c r="AO36">
         <v>0</v>
       </c>
@@ -6880,55 +6955,58 @@
         <v>0</v>
       </c>
       <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
         <v>40000</v>
       </c>
-      <c r="AT36">
+      <c r="AU36">
         <v>45000</v>
       </c>
-      <c r="AU36">
+      <c r="AV36">
         <v>40000</v>
       </c>
-      <c r="AV36">
+      <c r="AW36">
         <v>15</v>
       </c>
-      <c r="AW36">
+      <c r="AX36">
         <v>5</v>
       </c>
-      <c r="AX36">
+      <c r="AY36">
         <v>-5</v>
       </c>
-      <c r="AY36">
+      <c r="AZ36">
         <v>-15</v>
       </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
       <c r="BA36">
         <v>0</v>
       </c>
       <c r="BB36">
+        <v>0</v>
+      </c>
+      <c r="BC36">
         <v>1000</v>
       </c>
-      <c r="BC36">
+      <c r="BD36">
         <v>40</v>
       </c>
-      <c r="BD36">
+      <c r="BE36">
         <v>5</v>
       </c>
-      <c r="BE36">
+      <c r="BF36">
         <v>260</v>
       </c>
-      <c r="BF36">
+      <c r="BG36">
         <v>130</v>
       </c>
-      <c r="BG36">
+      <c r="BH36">
         <v>95</v>
       </c>
-      <c r="BH36">
+      <c r="BI36">
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:63" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:64" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>36</v>
       </c>
@@ -6944,42 +7022,39 @@
       <c r="F37">
         <v>1090</v>
       </c>
-      <c r="W37">
+      <c r="X37">
         <v>300</v>
       </c>
-      <c r="X37">
-        <v>1</v>
-      </c>
       <c r="Y37">
         <v>1</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="Z37">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="s">
         <v>169</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AB37" t="s">
         <v>170</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AC37" t="s">
         <v>171</v>
       </c>
-      <c r="AC37" t="s">
+      <c r="AD37" t="s">
         <v>172</v>
       </c>
-      <c r="AD37" s="10" t="s">
+      <c r="AE37" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AJ37">
+      <c r="AK37">
         <v>1500</v>
       </c>
-      <c r="AK37">
+      <c r="AL37">
         <v>-1</v>
       </c>
-      <c r="AL37">
+      <c r="AM37">
         <v>1500</v>
       </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
       <c r="AN37">
         <v>0</v>
       </c>
@@ -6996,64 +7071,67 @@
         <v>0</v>
       </c>
       <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
         <v>25000</v>
       </c>
-      <c r="AT37">
+      <c r="AU37">
         <v>30000</v>
       </c>
-      <c r="AU37">
+      <c r="AV37">
         <v>25000</v>
       </c>
-      <c r="AV37">
+      <c r="AW37">
         <v>15</v>
       </c>
-      <c r="AW37">
+      <c r="AX37">
         <v>5</v>
       </c>
-      <c r="AX37">
+      <c r="AY37">
         <v>-5</v>
       </c>
-      <c r="AY37">
+      <c r="AZ37">
         <v>-15</v>
       </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
       <c r="BA37">
         <v>0</v>
       </c>
       <c r="BB37">
+        <v>0</v>
+      </c>
+      <c r="BC37">
         <v>1500</v>
       </c>
-      <c r="BC37">
+      <c r="BD37">
         <v>40</v>
       </c>
-      <c r="BD37">
+      <c r="BE37">
         <v>5</v>
       </c>
-      <c r="BE37">
+      <c r="BF37">
         <v>260</v>
       </c>
-      <c r="BF37">
+      <c r="BG37">
         <v>130</v>
       </c>
-      <c r="BG37">
+      <c r="BH37">
         <v>95</v>
       </c>
-      <c r="BH37">
+      <c r="BI37">
         <v>60</v>
       </c>
-      <c r="BI37">
-        <v>1</v>
-      </c>
       <c r="BJ37">
+        <v>1</v>
+      </c>
+      <c r="BK37">
         <v>10</v>
       </c>
-      <c r="BK37">
+      <c r="BL37">
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>37</v>
       </c>
@@ -7069,25 +7147,22 @@
       <c r="F38">
         <v>1117</v>
       </c>
-      <c r="W38">
+      <c r="X38">
         <v>317</v>
       </c>
-      <c r="X38">
+      <c r="Y38">
         <v>12</v>
       </c>
-      <c r="Y38">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="s">
+      <c r="Z38">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="s">
         <v>174</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>175</v>
       </c>
-      <c r="AD38" s="10"/>
-      <c r="AJ38">
-        <v>0</v>
-      </c>
+      <c r="AE38" s="10"/>
       <c r="AK38">
         <v>0</v>
       </c>
@@ -7113,26 +7188,26 @@
         <v>0</v>
       </c>
       <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
         <v>35000</v>
       </c>
-      <c r="AT38">
+      <c r="AU38">
         <v>40000</v>
       </c>
-      <c r="AU38">
+      <c r="AV38">
         <v>35000</v>
       </c>
-      <c r="AV38">
+      <c r="AW38">
         <v>15</v>
       </c>
-      <c r="AW38">
-        <v>0</v>
-      </c>
       <c r="AX38">
+        <v>0</v>
+      </c>
+      <c r="AY38">
         <v>-15</v>
       </c>
-      <c r="AY38">
-        <v>0</v>
-      </c>
       <c r="AZ38">
         <v>0</v>
       </c>
@@ -7143,34 +7218,37 @@
         <v>0</v>
       </c>
       <c r="BC38">
+        <v>0</v>
+      </c>
+      <c r="BD38">
         <v>40</v>
       </c>
-      <c r="BD38">
+      <c r="BE38">
         <v>5</v>
       </c>
-      <c r="BE38">
+      <c r="BF38">
         <v>240</v>
       </c>
-      <c r="BF38">
+      <c r="BG38">
         <v>135</v>
       </c>
-      <c r="BG38">
+      <c r="BH38">
         <v>50</v>
       </c>
-      <c r="BH38">
-        <v>0</v>
-      </c>
       <c r="BI38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ38">
+        <v>1</v>
+      </c>
+      <c r="BK38">
         <v>10</v>
       </c>
-      <c r="BK38">
+      <c r="BL38">
         <v>1000</v>
       </c>
     </row>
-    <row r="39" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>38</v>
       </c>
@@ -7186,25 +7264,22 @@
       <c r="F39">
         <v>1118</v>
       </c>
-      <c r="W39">
+      <c r="X39">
         <v>318</v>
       </c>
-      <c r="X39">
+      <c r="Y39">
         <v>12</v>
       </c>
-      <c r="Y39">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="s">
+      <c r="Z39">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="s">
         <v>174</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AB39" t="s">
         <v>175</v>
       </c>
-      <c r="AD39" s="10"/>
-      <c r="AJ39">
-        <v>0</v>
-      </c>
+      <c r="AE39" s="10"/>
       <c r="AK39">
         <v>0</v>
       </c>
@@ -7230,26 +7305,26 @@
         <v>0</v>
       </c>
       <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
         <v>35000</v>
       </c>
-      <c r="AT39">
+      <c r="AU39">
         <v>40000</v>
       </c>
-      <c r="AU39">
+      <c r="AV39">
         <v>35000</v>
       </c>
-      <c r="AV39">
+      <c r="AW39">
         <v>15</v>
       </c>
-      <c r="AW39">
-        <v>0</v>
-      </c>
       <c r="AX39">
+        <v>0</v>
+      </c>
+      <c r="AY39">
         <v>-15</v>
       </c>
-      <c r="AY39">
-        <v>0</v>
-      </c>
       <c r="AZ39">
         <v>0</v>
       </c>
@@ -7260,34 +7335,37 @@
         <v>0</v>
       </c>
       <c r="BC39">
+        <v>0</v>
+      </c>
+      <c r="BD39">
         <v>40</v>
       </c>
-      <c r="BD39">
+      <c r="BE39">
         <v>5</v>
       </c>
-      <c r="BE39">
+      <c r="BF39">
         <v>240</v>
       </c>
-      <c r="BF39">
+      <c r="BG39">
         <v>135</v>
       </c>
-      <c r="BG39">
+      <c r="BH39">
         <v>50</v>
       </c>
-      <c r="BH39">
-        <v>0</v>
-      </c>
       <c r="BI39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ39">
+        <v>1</v>
+      </c>
+      <c r="BK39">
         <v>10</v>
       </c>
-      <c r="BK39">
+      <c r="BL39">
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>39</v>
       </c>
@@ -7303,25 +7381,22 @@
       <c r="F40">
         <v>1119</v>
       </c>
-      <c r="W40">
+      <c r="X40">
         <v>319</v>
       </c>
-      <c r="X40">
+      <c r="Y40">
         <v>12</v>
       </c>
-      <c r="Y40">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="s">
+      <c r="Z40">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="s">
         <v>174</v>
       </c>
-      <c r="AA40" t="s">
+      <c r="AB40" t="s">
         <v>175</v>
       </c>
-      <c r="AD40" s="10"/>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
+      <c r="AE40" s="10"/>
       <c r="AK40">
         <v>0</v>
       </c>
@@ -7347,26 +7422,26 @@
         <v>0</v>
       </c>
       <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
         <v>35000</v>
       </c>
-      <c r="AT40">
+      <c r="AU40">
         <v>40000</v>
       </c>
-      <c r="AU40">
+      <c r="AV40">
         <v>35000</v>
       </c>
-      <c r="AV40">
+      <c r="AW40">
         <v>15</v>
       </c>
-      <c r="AW40">
-        <v>0</v>
-      </c>
       <c r="AX40">
+        <v>0</v>
+      </c>
+      <c r="AY40">
         <v>-15</v>
       </c>
-      <c r="AY40">
-        <v>0</v>
-      </c>
       <c r="AZ40">
         <v>0</v>
       </c>
@@ -7377,34 +7452,37 @@
         <v>0</v>
       </c>
       <c r="BC40">
+        <v>0</v>
+      </c>
+      <c r="BD40">
         <v>40</v>
       </c>
-      <c r="BD40">
+      <c r="BE40">
         <v>5</v>
       </c>
-      <c r="BE40">
+      <c r="BF40">
         <v>240</v>
       </c>
-      <c r="BF40">
+      <c r="BG40">
         <v>135</v>
       </c>
-      <c r="BG40">
+      <c r="BH40">
         <v>50</v>
       </c>
-      <c r="BH40">
-        <v>0</v>
-      </c>
       <c r="BI40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ40">
+        <v>1</v>
+      </c>
+      <c r="BK40">
         <v>10</v>
       </c>
-      <c r="BK40">
+      <c r="BL40">
         <v>1000</v>
       </c>
     </row>
-    <row r="41" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>176</v>
       </c>
@@ -7429,54 +7507,51 @@
       <c r="M41">
         <v>1</v>
       </c>
-      <c r="W41">
+      <c r="X41">
         <v>320</v>
       </c>
-      <c r="X41">
-        <v>1</v>
-      </c>
       <c r="Y41">
         <v>1</v>
       </c>
-      <c r="Z41" t="s">
+      <c r="Z41">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="s">
         <v>176</v>
       </c>
-      <c r="AA41" t="s">
+      <c r="AB41" t="s">
         <v>177</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AC41" t="s">
         <v>178</v>
       </c>
-      <c r="AC41" t="s">
+      <c r="AD41" t="s">
         <v>179</v>
       </c>
-      <c r="AD41" s="10" t="s">
+      <c r="AE41" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="AE41" s="26">
+      <c r="AF41" s="26">
         <v>3390</v>
       </c>
-      <c r="AF41" s="2" t="s">
+      <c r="AG41" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="AG41" s="2" t="s">
+      <c r="AH41" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="AJ41">
+      <c r="AK41">
         <v>5000</v>
       </c>
-      <c r="AK41">
+      <c r="AL41">
         <v>-1</v>
       </c>
-      <c r="AL41">
+      <c r="AM41">
         <v>5000</v>
       </c>
-      <c r="AM41">
+      <c r="AN41">
         <v>100</v>
       </c>
-      <c r="AN41">
-        <v>0</v>
-      </c>
       <c r="AO41">
         <v>0</v>
       </c>
@@ -7490,55 +7565,58 @@
         <v>0</v>
       </c>
       <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
         <v>25000</v>
       </c>
-      <c r="AT41">
+      <c r="AU41">
         <v>30000</v>
       </c>
-      <c r="AU41">
+      <c r="AV41">
         <v>25000</v>
       </c>
-      <c r="AV41">
+      <c r="AW41">
         <v>15</v>
       </c>
-      <c r="AW41">
+      <c r="AX41">
         <v>5</v>
       </c>
-      <c r="AX41">
+      <c r="AY41">
         <v>-5</v>
       </c>
-      <c r="AY41">
+      <c r="AZ41">
         <v>-15</v>
       </c>
-      <c r="AZ41">
-        <v>0</v>
-      </c>
       <c r="BA41">
         <v>0</v>
       </c>
       <c r="BB41">
+        <v>0</v>
+      </c>
+      <c r="BC41">
         <v>1000</v>
       </c>
-      <c r="BC41">
+      <c r="BD41">
         <v>40</v>
       </c>
-      <c r="BD41">
+      <c r="BE41">
         <v>5</v>
       </c>
-      <c r="BE41">
+      <c r="BF41">
         <v>260</v>
       </c>
-      <c r="BF41">
+      <c r="BG41">
         <v>130</v>
       </c>
-      <c r="BG41">
+      <c r="BH41">
         <v>95</v>
       </c>
-      <c r="BH41">
+      <c r="BI41">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>181</v>
       </c>
@@ -7563,57 +7641,54 @@
       <c r="M42">
         <v>1</v>
       </c>
-      <c r="W42">
+      <c r="X42">
         <v>321</v>
       </c>
-      <c r="X42">
-        <v>1</v>
-      </c>
       <c r="Y42">
         <v>1</v>
       </c>
-      <c r="Z42" t="s">
+      <c r="Z42">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="s">
         <v>181</v>
       </c>
-      <c r="AA42" t="s">
+      <c r="AB42" t="s">
         <v>182</v>
       </c>
-      <c r="AB42" t="s">
+      <c r="AC42" t="s">
         <v>183</v>
       </c>
-      <c r="AC42" t="s">
+      <c r="AD42" t="s">
         <v>184</v>
       </c>
-      <c r="AD42" s="10" t="s">
+      <c r="AE42" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="AE42" s="26">
+      <c r="AF42" s="26">
         <v>3650</v>
       </c>
-      <c r="AF42" s="2" t="s">
+      <c r="AG42" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="AG42" s="2" t="s">
+      <c r="AH42" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="AH42" s="2" t="s">
+      <c r="AI42" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="AJ42">
+      <c r="AK42">
         <v>5000</v>
       </c>
-      <c r="AK42">
+      <c r="AL42">
         <v>-1</v>
       </c>
-      <c r="AL42">
+      <c r="AM42">
         <v>5000</v>
       </c>
-      <c r="AM42">
+      <c r="AN42">
         <v>100</v>
       </c>
-      <c r="AN42">
-        <v>0</v>
-      </c>
       <c r="AO42">
         <v>0</v>
       </c>
@@ -7627,7 +7702,7 @@
         <v>0</v>
       </c>
       <c r="AS42">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AT42">
         <v>50000</v>
@@ -7636,46 +7711,49 @@
         <v>50000</v>
       </c>
       <c r="AV42">
+        <v>50000</v>
+      </c>
+      <c r="AW42">
         <v>15</v>
       </c>
-      <c r="AW42">
+      <c r="AX42">
         <v>5</v>
       </c>
-      <c r="AX42">
+      <c r="AY42">
         <v>-5</v>
       </c>
-      <c r="AY42">
+      <c r="AZ42">
         <v>-15</v>
       </c>
-      <c r="AZ42">
-        <v>0</v>
-      </c>
       <c r="BA42">
         <v>0</v>
       </c>
       <c r="BB42">
+        <v>0</v>
+      </c>
+      <c r="BC42">
         <v>1000</v>
       </c>
-      <c r="BC42">
+      <c r="BD42">
         <v>40</v>
       </c>
-      <c r="BD42">
+      <c r="BE42">
         <v>5</v>
       </c>
-      <c r="BE42">
+      <c r="BF42">
         <v>260</v>
       </c>
-      <c r="BF42">
+      <c r="BG42">
         <v>130</v>
       </c>
-      <c r="BG42">
+      <c r="BH42">
         <v>95</v>
       </c>
-      <c r="BH42">
+      <c r="BI42">
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>186</v>
       </c>
@@ -7694,33 +7772,30 @@
       <c r="F43">
         <v>1245</v>
       </c>
-      <c r="W43">
+      <c r="X43">
         <v>322</v>
       </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
       <c r="Y43">
         <v>1</v>
       </c>
-      <c r="Z43" t="s">
+      <c r="Z43">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="s">
         <v>187</v>
       </c>
-      <c r="AA43" t="s">
+      <c r="AB43" t="s">
         <v>188</v>
       </c>
-      <c r="AB43" t="s">
+      <c r="AC43" t="s">
         <v>189</v>
       </c>
-      <c r="AC43" t="s">
+      <c r="AD43" t="s">
         <v>190</v>
       </c>
-      <c r="AD43" s="10" t="s">
+      <c r="AE43" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
       <c r="AK43">
         <v>0</v>
       </c>
@@ -7746,29 +7821,29 @@
         <v>0</v>
       </c>
       <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
         <v>25000</v>
       </c>
-      <c r="AT43">
+      <c r="AU43">
         <v>30000</v>
       </c>
-      <c r="AU43">
+      <c r="AV43">
         <v>25000</v>
       </c>
-      <c r="AV43">
+      <c r="AW43">
         <v>15</v>
       </c>
-      <c r="AW43">
+      <c r="AX43">
         <v>5</v>
       </c>
-      <c r="AX43">
+      <c r="AY43">
         <v>-5</v>
       </c>
-      <c r="AY43">
+      <c r="AZ43">
         <v>-15</v>
       </c>
-      <c r="AZ43">
-        <v>0</v>
-      </c>
       <c r="BA43">
         <v>0</v>
       </c>
@@ -7776,25 +7851,28 @@
         <v>0</v>
       </c>
       <c r="BC43">
+        <v>0</v>
+      </c>
+      <c r="BD43">
         <v>40</v>
       </c>
-      <c r="BD43">
+      <c r="BE43">
         <v>5</v>
       </c>
-      <c r="BE43">
+      <c r="BF43">
         <v>260</v>
       </c>
-      <c r="BF43">
+      <c r="BG43">
         <v>130</v>
       </c>
-      <c r="BG43">
+      <c r="BH43">
         <v>95</v>
       </c>
-      <c r="BH43">
+      <c r="BI43">
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>192</v>
       </c>
@@ -7813,51 +7891,48 @@
       <c r="F44">
         <v>1206</v>
       </c>
-      <c r="W44">
+      <c r="X44">
         <v>323</v>
       </c>
-      <c r="X44">
-        <v>1</v>
-      </c>
       <c r="Y44">
         <v>1</v>
       </c>
-      <c r="Z44" t="s">
+      <c r="Z44">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="s">
         <v>187</v>
       </c>
-      <c r="AA44" t="s">
+      <c r="AB44" t="s">
         <v>188</v>
       </c>
-      <c r="AB44" t="s">
+      <c r="AC44" t="s">
         <v>189</v>
       </c>
-      <c r="AC44" t="s">
+      <c r="AD44" t="s">
         <v>190</v>
       </c>
-      <c r="AD44" s="10" t="s">
+      <c r="AE44" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="AJ44">
+      <c r="AK44">
         <v>5000</v>
       </c>
-      <c r="AK44">
+      <c r="AL44">
         <v>-1</v>
       </c>
-      <c r="AL44">
+      <c r="AM44">
         <v>5000</v>
       </c>
-      <c r="AM44">
+      <c r="AN44">
         <v>100</v>
       </c>
-      <c r="AN44">
+      <c r="AO44">
         <v>40</v>
       </c>
-      <c r="AO44">
+      <c r="AP44">
         <v>20</v>
       </c>
-      <c r="AP44">
-        <v>0</v>
-      </c>
       <c r="AQ44">
         <v>0</v>
       </c>
@@ -7865,55 +7940,58 @@
         <v>0</v>
       </c>
       <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
         <v>25000</v>
       </c>
-      <c r="AT44">
+      <c r="AU44">
         <v>30000</v>
       </c>
-      <c r="AU44">
+      <c r="AV44">
         <v>25000</v>
       </c>
-      <c r="AV44">
+      <c r="AW44">
         <v>15</v>
       </c>
-      <c r="AW44">
+      <c r="AX44">
         <v>5</v>
       </c>
-      <c r="AX44">
+      <c r="AY44">
         <v>-5</v>
       </c>
-      <c r="AY44">
+      <c r="AZ44">
         <v>-15</v>
       </c>
-      <c r="AZ44">
-        <v>0</v>
-      </c>
       <c r="BA44">
         <v>0</v>
       </c>
       <c r="BB44">
+        <v>0</v>
+      </c>
+      <c r="BC44">
         <v>1000</v>
       </c>
-      <c r="BC44">
+      <c r="BD44">
         <v>40</v>
       </c>
-      <c r="BD44">
+      <c r="BE44">
         <v>5</v>
       </c>
-      <c r="BE44">
+      <c r="BF44">
         <v>260</v>
       </c>
-      <c r="BF44">
+      <c r="BG44">
         <v>130</v>
       </c>
-      <c r="BG44">
+      <c r="BH44">
         <v>95</v>
       </c>
-      <c r="BH44">
+      <c r="BI44">
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>193</v>
       </c>
@@ -7935,45 +8013,42 @@
       <c r="N45">
         <v>1</v>
       </c>
-      <c r="W45">
+      <c r="X45">
         <v>324</v>
       </c>
-      <c r="X45">
-        <v>1</v>
-      </c>
       <c r="Y45">
         <v>1</v>
       </c>
-      <c r="Z45" t="s">
+      <c r="Z45">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="s">
         <v>194</v>
       </c>
-      <c r="AA45" t="s">
+      <c r="AB45" t="s">
         <v>195</v>
       </c>
-      <c r="AB45" s="11" t="s">
+      <c r="AC45" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="AC45" s="12" t="s">
+      <c r="AD45" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="AD45" s="10" t="s">
+      <c r="AE45" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="AJ45">
+      <c r="AK45">
         <v>5000</v>
       </c>
-      <c r="AK45">
+      <c r="AL45">
         <v>-1</v>
       </c>
-      <c r="AL45">
+      <c r="AM45">
         <v>5000</v>
       </c>
-      <c r="AM45">
+      <c r="AN45">
         <v>100</v>
       </c>
-      <c r="AN45">
-        <v>0</v>
-      </c>
       <c r="AO45">
         <v>0</v>
       </c>
@@ -7987,55 +8062,58 @@
         <v>0</v>
       </c>
       <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
         <v>25000</v>
       </c>
-      <c r="AT45">
+      <c r="AU45">
         <v>30000</v>
       </c>
-      <c r="AU45">
+      <c r="AV45">
         <v>25000</v>
       </c>
-      <c r="AV45">
+      <c r="AW45">
         <v>15</v>
       </c>
-      <c r="AW45">
+      <c r="AX45">
         <v>5</v>
       </c>
-      <c r="AX45">
+      <c r="AY45">
         <v>-5</v>
       </c>
-      <c r="AY45">
+      <c r="AZ45">
         <v>-15</v>
       </c>
-      <c r="AZ45">
-        <v>0</v>
-      </c>
       <c r="BA45">
         <v>0</v>
       </c>
       <c r="BB45">
+        <v>0</v>
+      </c>
+      <c r="BC45">
         <v>1000</v>
       </c>
-      <c r="BC45">
+      <c r="BD45">
         <v>40</v>
       </c>
-      <c r="BD45">
+      <c r="BE45">
         <v>5</v>
       </c>
-      <c r="BE45">
+      <c r="BF45">
         <v>260</v>
       </c>
-      <c r="BF45">
+      <c r="BG45">
         <v>130</v>
       </c>
-      <c r="BG45">
+      <c r="BH45">
         <v>95</v>
       </c>
-      <c r="BH45">
+      <c r="BI45">
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>199</v>
       </c>
@@ -8057,57 +8135,54 @@
       <c r="O46">
         <v>1</v>
       </c>
-      <c r="W46">
+      <c r="X46">
         <v>325</v>
       </c>
-      <c r="X46">
-        <v>1</v>
-      </c>
       <c r="Y46">
         <v>1</v>
       </c>
-      <c r="Z46" t="s">
+      <c r="Z46">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="s">
         <v>200</v>
       </c>
-      <c r="AA46" t="s">
+      <c r="AB46" t="s">
         <v>201</v>
       </c>
-      <c r="AB46" s="11" t="s">
+      <c r="AC46" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="AC46" s="12" t="s">
+      <c r="AD46" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="AD46" s="10" t="s">
+      <c r="AE46" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="AE46" s="26">
+      <c r="AF46" s="26">
         <v>3528</v>
       </c>
-      <c r="AF46" s="2" t="s">
+      <c r="AG46" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="AG46" s="2" t="s">
+      <c r="AH46" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="AH46" s="2" t="s">
+      <c r="AI46" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="AJ46">
+      <c r="AK46">
         <v>5000</v>
       </c>
-      <c r="AK46">
+      <c r="AL46">
         <v>-1</v>
       </c>
-      <c r="AL46">
+      <c r="AM46">
         <v>5000</v>
       </c>
-      <c r="AM46">
+      <c r="AN46">
         <v>100</v>
       </c>
-      <c r="AN46">
-        <v>0</v>
-      </c>
       <c r="AO46">
         <v>0</v>
       </c>
@@ -8121,55 +8196,58 @@
         <v>0</v>
       </c>
       <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
         <v>25000</v>
       </c>
-      <c r="AT46">
+      <c r="AU46">
         <v>30000</v>
       </c>
-      <c r="AU46">
+      <c r="AV46">
         <v>25000</v>
       </c>
-      <c r="AV46">
+      <c r="AW46">
         <v>15</v>
       </c>
-      <c r="AW46">
+      <c r="AX46">
         <v>5</v>
       </c>
-      <c r="AX46">
+      <c r="AY46">
         <v>-5</v>
       </c>
-      <c r="AY46">
+      <c r="AZ46">
         <v>-15</v>
       </c>
-      <c r="AZ46">
-        <v>0</v>
-      </c>
       <c r="BA46">
         <v>0</v>
       </c>
       <c r="BB46">
+        <v>0</v>
+      </c>
+      <c r="BC46">
         <v>1000</v>
       </c>
-      <c r="BC46">
+      <c r="BD46">
         <v>40</v>
       </c>
-      <c r="BD46">
+      <c r="BE46">
         <v>5</v>
       </c>
-      <c r="BE46">
+      <c r="BF46">
         <v>260</v>
       </c>
-      <c r="BF46">
+      <c r="BG46">
         <v>130</v>
       </c>
-      <c r="BG46">
+      <c r="BH46">
         <v>95</v>
       </c>
-      <c r="BH46">
+      <c r="BI46">
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>205</v>
       </c>
@@ -8191,55 +8269,52 @@
       <c r="P47">
         <v>1</v>
       </c>
-      <c r="W47">
+      <c r="X47">
         <v>326</v>
       </c>
-      <c r="X47">
-        <v>1</v>
-      </c>
       <c r="Y47">
         <v>1</v>
       </c>
-      <c r="Z47" t="s">
+      <c r="Z47">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="s">
         <v>206</v>
       </c>
-      <c r="AA47" t="s">
+      <c r="AB47" t="s">
         <v>207</v>
       </c>
-      <c r="AB47" s="13" t="s">
+      <c r="AC47" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AC47" s="14" t="s">
+      <c r="AD47" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="AD47" s="10" t="s">
+      <c r="AE47" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="AE47" s="26">
+      <c r="AF47" s="26">
         <v>3588</v>
       </c>
-      <c r="AF47" s="2" t="s">
+      <c r="AG47" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="AG47" s="2" t="s">
+      <c r="AH47" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="AH47" s="2"/>
-      <c r="AJ47">
+      <c r="AI47" s="2"/>
+      <c r="AK47">
         <v>5000</v>
       </c>
-      <c r="AK47">
+      <c r="AL47">
         <v>-1</v>
       </c>
-      <c r="AL47">
+      <c r="AM47">
         <v>5000</v>
       </c>
-      <c r="AM47">
+      <c r="AN47">
         <v>100</v>
       </c>
-      <c r="AN47">
-        <v>0</v>
-      </c>
       <c r="AO47">
         <v>0</v>
       </c>
@@ -8253,55 +8328,58 @@
         <v>0</v>
       </c>
       <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
         <v>25000</v>
       </c>
-      <c r="AT47">
+      <c r="AU47">
         <v>30000</v>
       </c>
-      <c r="AU47">
+      <c r="AV47">
         <v>25000</v>
       </c>
-      <c r="AV47">
+      <c r="AW47">
         <v>15</v>
       </c>
-      <c r="AW47">
+      <c r="AX47">
         <v>5</v>
       </c>
-      <c r="AX47">
+      <c r="AY47">
         <v>-5</v>
       </c>
-      <c r="AY47">
+      <c r="AZ47">
         <v>-15</v>
       </c>
-      <c r="AZ47">
-        <v>0</v>
-      </c>
       <c r="BA47">
         <v>0</v>
       </c>
       <c r="BB47">
+        <v>0</v>
+      </c>
+      <c r="BC47">
         <v>1000</v>
       </c>
-      <c r="BC47">
+      <c r="BD47">
         <v>40</v>
       </c>
-      <c r="BD47">
+      <c r="BE47">
         <v>5</v>
       </c>
-      <c r="BE47">
+      <c r="BF47">
         <v>260</v>
       </c>
-      <c r="BF47">
+      <c r="BG47">
         <v>130</v>
       </c>
-      <c r="BG47">
+      <c r="BH47">
         <v>95</v>
       </c>
-      <c r="BH47">
+      <c r="BI47">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>211</v>
       </c>
@@ -8323,55 +8401,52 @@
       <c r="Q48">
         <v>1</v>
       </c>
-      <c r="W48">
+      <c r="X48">
         <v>327</v>
       </c>
-      <c r="X48">
-        <v>1</v>
-      </c>
       <c r="Y48">
         <v>1</v>
       </c>
-      <c r="Z48" t="s">
+      <c r="Z48">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="s">
         <v>211</v>
       </c>
-      <c r="AA48" t="s">
+      <c r="AB48" t="s">
         <v>212</v>
       </c>
-      <c r="AB48" s="15" t="s">
+      <c r="AC48" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="AC48" s="15" t="s">
+      <c r="AD48" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="AD48" s="15" t="s">
+      <c r="AE48" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="AE48" s="27">
+      <c r="AF48" s="27">
         <v>3705</v>
       </c>
-      <c r="AF48" s="2" t="s">
+      <c r="AG48" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="AG48" s="2" t="s">
+      <c r="AH48" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="AH48" s="2"/>
-      <c r="AJ48">
+      <c r="AI48" s="2"/>
+      <c r="AK48">
         <v>5000</v>
       </c>
-      <c r="AK48">
+      <c r="AL48">
         <v>-1</v>
       </c>
-      <c r="AL48">
+      <c r="AM48">
         <v>5000</v>
       </c>
-      <c r="AM48">
+      <c r="AN48">
         <v>100</v>
       </c>
-      <c r="AN48">
-        <v>0</v>
-      </c>
       <c r="AO48">
         <v>0</v>
       </c>
@@ -8385,55 +8460,58 @@
         <v>0</v>
       </c>
       <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
         <v>25000</v>
       </c>
-      <c r="AT48">
+      <c r="AU48">
         <v>30000</v>
       </c>
-      <c r="AU48">
+      <c r="AV48">
         <v>25000</v>
       </c>
-      <c r="AV48">
+      <c r="AW48">
         <v>15</v>
       </c>
-      <c r="AW48">
+      <c r="AX48">
         <v>5</v>
       </c>
-      <c r="AX48">
+      <c r="AY48">
         <v>-5</v>
       </c>
-      <c r="AY48">
+      <c r="AZ48">
         <v>-15</v>
       </c>
-      <c r="AZ48">
-        <v>0</v>
-      </c>
       <c r="BA48">
         <v>0</v>
       </c>
       <c r="BB48">
+        <v>0</v>
+      </c>
+      <c r="BC48">
         <v>1000</v>
       </c>
-      <c r="BC48">
+      <c r="BD48">
         <v>40</v>
       </c>
-      <c r="BD48">
+      <c r="BE48">
         <v>5</v>
       </c>
-      <c r="BE48">
+      <c r="BF48">
         <v>260</v>
       </c>
-      <c r="BF48">
+      <c r="BG48">
         <v>130</v>
       </c>
-      <c r="BG48">
+      <c r="BH48">
         <v>95</v>
       </c>
-      <c r="BH48">
+      <c r="BI48">
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>216</v>
       </c>
@@ -8455,57 +8533,54 @@
       <c r="R49">
         <v>1</v>
       </c>
-      <c r="W49">
+      <c r="X49">
         <v>328</v>
       </c>
-      <c r="X49">
-        <v>1</v>
-      </c>
       <c r="Y49">
         <v>1</v>
       </c>
-      <c r="Z49" t="s">
+      <c r="Z49">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="s">
         <v>216</v>
       </c>
-      <c r="AA49" t="s">
+      <c r="AB49" t="s">
         <v>217</v>
       </c>
-      <c r="AB49" s="16" t="s">
+      <c r="AC49" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="AC49" s="17" t="s">
+      <c r="AD49" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="AD49" s="17" t="s">
+      <c r="AE49" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="AE49" s="27">
+      <c r="AF49" s="27">
         <v>3857</v>
       </c>
-      <c r="AF49" s="2" t="s">
+      <c r="AG49" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="AG49" s="2" t="s">
+      <c r="AH49" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="AH49" s="2" t="s">
+      <c r="AI49" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="AJ49">
+      <c r="AK49">
         <v>5000</v>
       </c>
-      <c r="AK49">
+      <c r="AL49">
         <v>-1</v>
       </c>
-      <c r="AL49">
+      <c r="AM49">
         <v>5000</v>
       </c>
-      <c r="AM49">
+      <c r="AN49">
         <v>100</v>
       </c>
-      <c r="AN49">
-        <v>0</v>
-      </c>
       <c r="AO49">
         <v>0</v>
       </c>
@@ -8519,55 +8594,58 @@
         <v>0</v>
       </c>
       <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
         <v>50000</v>
       </c>
-      <c r="AT49">
+      <c r="AU49">
         <v>55000</v>
       </c>
-      <c r="AU49">
+      <c r="AV49">
         <v>50000</v>
       </c>
-      <c r="AV49">
+      <c r="AW49">
         <v>15</v>
       </c>
-      <c r="AW49">
+      <c r="AX49">
         <v>5</v>
       </c>
-      <c r="AX49">
+      <c r="AY49">
         <v>-5</v>
       </c>
-      <c r="AY49">
+      <c r="AZ49">
         <v>-15</v>
       </c>
-      <c r="AZ49">
-        <v>0</v>
-      </c>
       <c r="BA49">
         <v>0</v>
       </c>
       <c r="BB49">
+        <v>0</v>
+      </c>
+      <c r="BC49">
         <v>1000</v>
       </c>
-      <c r="BC49">
+      <c r="BD49">
         <v>40</v>
       </c>
-      <c r="BD49">
+      <c r="BE49">
         <v>5</v>
       </c>
-      <c r="BE49">
+      <c r="BF49">
         <v>260</v>
       </c>
-      <c r="BF49">
+      <c r="BG49">
         <v>130</v>
       </c>
-      <c r="BG49">
+      <c r="BH49">
         <v>95</v>
       </c>
-      <c r="BH49">
+      <c r="BI49">
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>221</v>
       </c>
@@ -8589,57 +8667,54 @@
       <c r="S50">
         <v>1</v>
       </c>
-      <c r="W50">
+      <c r="X50">
         <v>329</v>
       </c>
-      <c r="X50">
-        <v>1</v>
-      </c>
       <c r="Y50">
         <v>1</v>
       </c>
-      <c r="Z50" t="s">
+      <c r="Z50">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="s">
         <v>221</v>
       </c>
-      <c r="AA50" t="s">
+      <c r="AB50" t="s">
         <v>222</v>
       </c>
-      <c r="AB50" s="18" t="s">
+      <c r="AC50" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="AC50" s="15" t="s">
+      <c r="AD50" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="AD50" s="15" t="s">
+      <c r="AE50" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="AE50" s="27">
+      <c r="AF50" s="27">
         <v>3987</v>
       </c>
-      <c r="AF50" s="2" t="s">
+      <c r="AG50" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="AG50" s="2" t="s">
+      <c r="AH50" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AH50" s="2" t="s">
+      <c r="AI50" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="AJ50">
+      <c r="AK50">
         <v>5000</v>
       </c>
-      <c r="AK50">
+      <c r="AL50">
         <v>-1</v>
       </c>
-      <c r="AL50">
+      <c r="AM50">
         <v>5000</v>
       </c>
-      <c r="AM50">
+      <c r="AN50">
         <v>100</v>
       </c>
-      <c r="AN50">
-        <v>0</v>
-      </c>
       <c r="AO50">
         <v>0</v>
       </c>
@@ -8653,55 +8728,58 @@
         <v>0</v>
       </c>
       <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
         <v>25000</v>
       </c>
-      <c r="AT50">
+      <c r="AU50">
         <v>30000</v>
       </c>
-      <c r="AU50">
+      <c r="AV50">
         <v>25000</v>
       </c>
-      <c r="AV50">
+      <c r="AW50">
         <v>15</v>
       </c>
-      <c r="AW50">
+      <c r="AX50">
         <v>5</v>
       </c>
-      <c r="AX50">
+      <c r="AY50">
         <v>-5</v>
       </c>
-      <c r="AY50">
+      <c r="AZ50">
         <v>-15</v>
       </c>
-      <c r="AZ50">
-        <v>0</v>
-      </c>
       <c r="BA50">
         <v>0</v>
       </c>
       <c r="BB50">
+        <v>0</v>
+      </c>
+      <c r="BC50">
         <v>1000</v>
       </c>
-      <c r="BC50">
+      <c r="BD50">
         <v>40</v>
       </c>
-      <c r="BD50">
+      <c r="BE50">
         <v>5</v>
       </c>
-      <c r="BE50">
+      <c r="BF50">
         <v>260</v>
       </c>
-      <c r="BF50">
+      <c r="BG50">
         <v>130</v>
       </c>
-      <c r="BG50">
+      <c r="BH50">
         <v>95</v>
       </c>
-      <c r="BH50">
+      <c r="BI50">
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>226</v>
       </c>
@@ -8723,57 +8801,54 @@
       <c r="T51">
         <v>1</v>
       </c>
-      <c r="W51">
+      <c r="X51">
         <v>330</v>
       </c>
-      <c r="X51">
-        <v>1</v>
-      </c>
       <c r="Y51">
         <v>1</v>
       </c>
-      <c r="Z51" s="8" t="s">
+      <c r="Z51">
+        <v>1</v>
+      </c>
+      <c r="AA51" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="AA51" s="8" t="s">
+      <c r="AB51" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="AB51" s="19" t="s">
+      <c r="AC51" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="AC51" s="20" t="s">
+      <c r="AD51" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="AD51" s="21" t="s">
+      <c r="AE51" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="AE51" s="26">
+      <c r="AF51" s="26">
         <v>4208</v>
       </c>
-      <c r="AF51" s="2" t="s">
+      <c r="AG51" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="AG51" s="2" t="s">
+      <c r="AH51" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="AH51" s="2" t="s">
+      <c r="AI51" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="AJ51">
+      <c r="AK51">
         <v>5000</v>
       </c>
-      <c r="AK51">
+      <c r="AL51">
         <v>-1</v>
       </c>
-      <c r="AL51">
+      <c r="AM51">
         <v>5000</v>
       </c>
-      <c r="AM51">
+      <c r="AN51">
         <v>100</v>
       </c>
-      <c r="AN51">
-        <v>0</v>
-      </c>
       <c r="AO51">
         <v>0</v>
       </c>
@@ -8787,55 +8862,58 @@
         <v>0</v>
       </c>
       <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
         <v>25000</v>
       </c>
-      <c r="AT51">
+      <c r="AU51">
         <v>30000</v>
       </c>
-      <c r="AU51">
+      <c r="AV51">
         <v>25000</v>
       </c>
-      <c r="AV51">
+      <c r="AW51">
         <v>15</v>
       </c>
-      <c r="AW51">
+      <c r="AX51">
         <v>5</v>
       </c>
-      <c r="AX51">
+      <c r="AY51">
         <v>-5</v>
       </c>
-      <c r="AY51">
+      <c r="AZ51">
         <v>-15</v>
       </c>
-      <c r="AZ51">
-        <v>0</v>
-      </c>
       <c r="BA51">
         <v>0</v>
       </c>
       <c r="BB51">
+        <v>0</v>
+      </c>
+      <c r="BC51">
         <v>1000</v>
       </c>
-      <c r="BC51">
+      <c r="BD51">
         <v>40</v>
       </c>
-      <c r="BD51">
+      <c r="BE51">
         <v>5</v>
       </c>
-      <c r="BE51">
+      <c r="BF51">
         <v>260</v>
       </c>
-      <c r="BF51">
+      <c r="BG51">
         <v>130</v>
       </c>
-      <c r="BG51">
+      <c r="BH51">
         <v>95</v>
       </c>
-      <c r="BH51">
+      <c r="BI51">
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:60" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>467</v>
       </c>
@@ -8860,57 +8938,54 @@
       <c r="U52">
         <v>1</v>
       </c>
-      <c r="W52">
+      <c r="X52">
         <v>331</v>
       </c>
-      <c r="X52">
-        <v>1</v>
-      </c>
       <c r="Y52">
         <v>1</v>
       </c>
-      <c r="Z52" s="2" t="s">
+      <c r="Z52">
+        <v>1</v>
+      </c>
+      <c r="AA52" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="AA52" s="2" t="s">
+      <c r="AB52" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="AB52" s="21" t="s">
+      <c r="AC52" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="AC52" s="21" t="s">
+      <c r="AD52" s="21" t="s">
         <v>472</v>
       </c>
-      <c r="AD52" s="21" t="s">
+      <c r="AE52" s="21" t="s">
         <v>473</v>
       </c>
-      <c r="AE52" s="35">
+      <c r="AF52" s="35">
         <v>20194</v>
       </c>
-      <c r="AF52" s="2" t="s">
+      <c r="AG52" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="AG52" s="2" t="s">
+      <c r="AH52" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="AH52" s="2" t="s">
+      <c r="AI52" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="AJ52">
+      <c r="AK52">
         <v>5000</v>
       </c>
-      <c r="AK52">
+      <c r="AL52">
         <v>-1</v>
       </c>
-      <c r="AL52">
+      <c r="AM52">
         <v>5000</v>
       </c>
-      <c r="AM52">
+      <c r="AN52">
         <v>100</v>
       </c>
-      <c r="AN52">
-        <v>0</v>
-      </c>
       <c r="AO52">
         <v>0</v>
       </c>
@@ -8924,55 +8999,58 @@
         <v>0</v>
       </c>
       <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
         <v>25000</v>
       </c>
-      <c r="AT52">
+      <c r="AU52">
         <v>30000</v>
       </c>
-      <c r="AU52">
+      <c r="AV52">
         <v>25000</v>
       </c>
-      <c r="AV52">
+      <c r="AW52">
         <v>15</v>
       </c>
-      <c r="AW52">
+      <c r="AX52">
         <v>5</v>
       </c>
-      <c r="AX52">
+      <c r="AY52">
         <v>-5</v>
       </c>
-      <c r="AY52">
+      <c r="AZ52">
         <v>-15</v>
       </c>
-      <c r="AZ52">
-        <v>0</v>
-      </c>
       <c r="BA52">
         <v>0</v>
       </c>
       <c r="BB52">
+        <v>0</v>
+      </c>
+      <c r="BC52">
         <v>1000</v>
       </c>
-      <c r="BC52">
+      <c r="BD52">
         <v>40</v>
       </c>
-      <c r="BD52">
+      <c r="BE52">
         <v>5</v>
       </c>
-      <c r="BE52">
+      <c r="BF52">
         <v>260</v>
       </c>
-      <c r="BF52">
+      <c r="BG52">
         <v>130</v>
       </c>
-      <c r="BG52">
+      <c r="BH52">
         <v>95</v>
       </c>
-      <c r="BH52">
+      <c r="BI52">
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>502</v>
       </c>
@@ -8994,45 +9072,42 @@
       <c r="V53">
         <v>1</v>
       </c>
-      <c r="W53">
+      <c r="X53">
         <v>332</v>
       </c>
-      <c r="X53">
-        <v>1</v>
-      </c>
       <c r="Y53">
         <v>1</v>
       </c>
-      <c r="Z53" s="2" t="s">
+      <c r="Z53">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="AA53" s="2" t="s">
+      <c r="AB53" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="AB53" s="37" t="s">
+      <c r="AC53" s="37" t="s">
         <v>507</v>
       </c>
-      <c r="AC53" s="38" t="s">
+      <c r="AD53" s="38" t="s">
         <v>508</v>
       </c>
-      <c r="AD53" s="38" t="s">
+      <c r="AE53" s="38" t="s">
         <v>509</v>
       </c>
-      <c r="AJ53">
+      <c r="AK53">
         <v>5000</v>
       </c>
-      <c r="AK53">
+      <c r="AL53">
         <v>-1</v>
       </c>
-      <c r="AL53">
+      <c r="AM53">
         <v>5000</v>
       </c>
-      <c r="AM53">
+      <c r="AN53">
         <v>100</v>
       </c>
-      <c r="AN53">
-        <v>0</v>
-      </c>
       <c r="AO53">
         <v>0</v>
       </c>
@@ -9046,110 +9121,241 @@
         <v>0</v>
       </c>
       <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
         <v>25000</v>
       </c>
-      <c r="AT53">
+      <c r="AU53">
         <v>30000</v>
       </c>
-      <c r="AU53">
+      <c r="AV53">
         <v>25000</v>
       </c>
-      <c r="AV53">
+      <c r="AW53">
         <v>15</v>
       </c>
-      <c r="AW53">
+      <c r="AX53">
         <v>5</v>
       </c>
-      <c r="AX53">
+      <c r="AY53">
         <v>-5</v>
       </c>
-      <c r="AY53">
+      <c r="AZ53">
         <v>-15</v>
       </c>
-      <c r="AZ53">
-        <v>0</v>
-      </c>
       <c r="BA53">
         <v>0</v>
       </c>
       <c r="BB53">
+        <v>0</v>
+      </c>
+      <c r="BC53">
         <v>1000</v>
       </c>
-      <c r="BC53">
+      <c r="BD53">
         <v>40</v>
       </c>
-      <c r="BD53">
+      <c r="BE53">
         <v>5</v>
       </c>
-      <c r="BE53">
+      <c r="BF53">
         <v>260</v>
       </c>
-      <c r="BF53">
+      <c r="BG53">
         <v>130</v>
       </c>
-      <c r="BG53">
+      <c r="BH53">
         <v>95</v>
       </c>
-      <c r="BH53">
+      <c r="BI53">
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="AG54" s="2"/>
-    </row>
-    <row r="55" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="AG55" s="2"/>
-    </row>
-    <row r="56" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="AF56" s="2"/>
-    </row>
-    <row r="65" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF65" s="2"/>
-    </row>
-    <row r="66" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF66" s="2"/>
-    </row>
-    <row r="67" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF67" s="2"/>
-    </row>
-    <row r="68" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AE68" s="26"/>
-      <c r="AF68" s="2"/>
-    </row>
-    <row r="69" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF69" s="2"/>
-    </row>
-    <row r="70" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF70" s="2"/>
-    </row>
-    <row r="71" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF71" s="2"/>
-    </row>
-    <row r="72" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AE72" s="26"/>
-      <c r="AF72" s="2"/>
-    </row>
-    <row r="73" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF73" s="2"/>
-    </row>
-    <row r="74" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF74" s="2"/>
-    </row>
-    <row r="75" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF75" s="2"/>
-    </row>
-    <row r="76" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AE76" s="26"/>
-      <c r="AF76" s="2"/>
-    </row>
-    <row r="77" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF77" s="2"/>
-    </row>
-    <row r="78" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF78" s="2"/>
-    </row>
-    <row r="79" spans="31:32" x14ac:dyDescent="0.2">
-      <c r="AF79" s="2"/>
+    <row r="54" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B54">
+        <v>53</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>23</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>251005</v>
+      </c>
+      <c r="W54">
+        <v>1</v>
+      </c>
+      <c r="X54">
+        <v>333</v>
+      </c>
+      <c r="Y54">
+        <v>1</v>
+      </c>
+      <c r="Z54">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AB54" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AC54" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="AD54" s="50" t="s">
+        <v>518</v>
+      </c>
+      <c r="AE54" s="50" t="s">
+        <v>519</v>
+      </c>
+      <c r="AF54" s="25">
+        <v>25101013</v>
+      </c>
+      <c r="AG54" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="AH54" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="AK54">
+        <v>5000</v>
+      </c>
+      <c r="AL54">
+        <v>-1</v>
+      </c>
+      <c r="AM54">
+        <v>5000</v>
+      </c>
+      <c r="AN54">
+        <v>100</v>
+      </c>
+      <c r="AO54">
+        <v>0</v>
+      </c>
+      <c r="AP54">
+        <v>0</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>25000</v>
+      </c>
+      <c r="AU54">
+        <v>30000</v>
+      </c>
+      <c r="AV54">
+        <v>25000</v>
+      </c>
+      <c r="AW54">
+        <v>15</v>
+      </c>
+      <c r="AX54">
+        <v>5</v>
+      </c>
+      <c r="AY54">
+        <v>-5</v>
+      </c>
+      <c r="AZ54">
+        <v>-15</v>
+      </c>
+      <c r="BA54">
+        <v>0</v>
+      </c>
+      <c r="BB54">
+        <v>0</v>
+      </c>
+      <c r="BC54">
+        <v>1000</v>
+      </c>
+      <c r="BD54">
+        <v>40</v>
+      </c>
+      <c r="BE54">
+        <v>5</v>
+      </c>
+      <c r="BF54">
+        <v>260</v>
+      </c>
+      <c r="BG54">
+        <v>130</v>
+      </c>
+      <c r="BH54">
+        <v>95</v>
+      </c>
+      <c r="BI54">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="AH55" s="2"/>
+    </row>
+    <row r="56" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="AG56" s="2"/>
+    </row>
+    <row r="65" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG65" s="2"/>
+    </row>
+    <row r="66" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG66" s="2"/>
+    </row>
+    <row r="67" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG67" s="2"/>
+    </row>
+    <row r="68" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AF68" s="26"/>
+      <c r="AG68" s="2"/>
+    </row>
+    <row r="69" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG69" s="2"/>
+    </row>
+    <row r="70" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG70" s="2"/>
+    </row>
+    <row r="71" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG71" s="2"/>
+    </row>
+    <row r="72" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AF72" s="26"/>
+      <c r="AG72" s="2"/>
+    </row>
+    <row r="73" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG73" s="2"/>
+    </row>
+    <row r="74" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG74" s="2"/>
+    </row>
+    <row r="75" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG75" s="2"/>
+    </row>
+    <row r="76" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AF76" s="26"/>
+      <c r="AG76" s="2"/>
+    </row>
+    <row r="77" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG77" s="2"/>
+    </row>
+    <row r="78" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG78" s="2"/>
+    </row>
+    <row r="79" spans="32:33" x14ac:dyDescent="0.2">
+      <c r="AG79" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
@@ -9877,7 +10083,7 @@
     <col min="3" max="3" width="23.5" customWidth="1"/>
     <col min="4" max="4" width="13.75" style="25" customWidth="1"/>
     <col min="5" max="5" width="10.125" style="25" customWidth="1"/>
-    <col min="6" max="6" width="9" style="25"/>
+    <col min="6" max="6" width="9.5" style="25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.125" style="25" customWidth="1"/>
     <col min="8" max="9" width="28.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
@@ -10372,6 +10578,33 @@
       <c r="H18" s="2" t="s">
         <v>506</v>
       </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="46" t="s">
+        <v>512</v>
+      </c>
+      <c r="B19" s="47">
+        <v>16</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>513</v>
+      </c>
+      <c r="D19" s="48">
+        <v>16</v>
+      </c>
+      <c r="E19" s="49">
+        <v>25101012</v>
+      </c>
+      <c r="F19" s="49">
+        <v>25101014</v>
+      </c>
+      <c r="G19" s="48">
+        <v>1</v>
+      </c>
+      <c r="H19" s="46" t="s">
+        <v>516</v>
+      </c>
+      <c r="I19" s="47"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C23" s="2"/>

--- a/source/bin/excel/desktop.xlsx
+++ b/source/bin/excel/desktop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4044106B-90FF-47E9-9E9D-52ADA9674A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBD032C-AB0E-44E2-980A-517DF4D8AF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="885" yWindow="-120" windowWidth="28035" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -37,8 +37,48 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>李晓楠</author>
+  </authors>
+  <commentList>
+    <comment ref="Y2" authorId="0" shapeId="0" xr:uid="{DFF06CB9-46CA-4E9B-A6A9-B93CAE41BB39}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>李晓楠:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0：一局战
+1：四麻东
+2：四麻南
+11：三麻东
+12：三麻南</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="523">
   <si>
     <t>sheet</t>
   </si>
@@ -71,9 +111,6 @@
   </si>
   <si>
     <t>settings</t>
-  </si>
-  <si>
-    <t>kv</t>
   </si>
   <si>
     <t>简单设定字段</t>
@@ -1766,12 +1803,20 @@
     <t>逆襲の戦</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>对局模式</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>下剋上</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1908,6 +1953,21 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2521,15 +2581,15 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -2540,7 +2600,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -2549,12 +2609,12 @@
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -2563,7 +2623,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="5:5" x14ac:dyDescent="0.2">
@@ -2622,7 +2682,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BL79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2666,540 +2726,540 @@
   <sheetData>
     <row r="1" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
       </c>
       <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>17</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>25</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>26</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>30</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>31</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="X1" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AF1" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>311</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AK1" t="s">
         <v>41</v>
       </c>
-      <c r="AF1" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>312</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>42</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>43</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>44</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>45</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>46</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>47</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>48</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>49</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>50</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>51</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>52</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>53</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>54</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>55</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>56</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>57</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>58</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>59</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>60</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>61</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>62</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>63</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>64</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>65</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>66</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>67</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>68</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>72</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>73</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>74</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>75</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>76</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>77</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>78</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>79</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>80</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>81</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>82</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>83</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q2" t="s">
         <v>84</v>
       </c>
-      <c r="P2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>85</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="X2" t="s">
         <v>86</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="X2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="Z2" t="s">
         <v>88</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>89</v>
       </c>
       <c r="AE2" s="10"/>
       <c r="AF2" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="AG2" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="AH2" t="s">
         <v>319</v>
       </c>
-      <c r="AG2" s="22" t="s">
-        <v>490</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>320</v>
-      </c>
       <c r="AK2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL2" t="s">
         <v>90</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>91</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>92</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>93</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>94</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>95</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>96</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>97</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>98</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>99</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>100</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>101</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>102</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>103</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>104</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>105</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>106</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>107</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>108</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>109</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>110</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BJ2" t="s">
         <v>111</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>112</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>113</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
         <v>115</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N3" t="s">
+        <v>115</v>
+      </c>
+      <c r="O3" t="s">
+        <v>115</v>
+      </c>
+      <c r="P3" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>115</v>
+      </c>
+      <c r="R3" t="s">
+        <v>115</v>
+      </c>
+      <c r="S3" t="s">
+        <v>115</v>
+      </c>
+      <c r="T3" t="s">
+        <v>115</v>
+      </c>
+      <c r="U3" t="s">
+        <v>115</v>
+      </c>
+      <c r="V3" t="s">
+        <v>115</v>
+      </c>
+      <c r="W3" t="s">
+        <v>115</v>
+      </c>
+      <c r="X3" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA3" t="s">
         <v>116</v>
       </c>
-      <c r="C3" t="s">
+      <c r="AB3" t="s">
         <v>116</v>
       </c>
-      <c r="D3" t="s">
+      <c r="AC3" t="s">
         <v>116</v>
       </c>
-      <c r="E3" t="s">
+      <c r="AD3" t="s">
         <v>116</v>
       </c>
-      <c r="F3" t="s">
+      <c r="AE3" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="G3" t="s">
+      <c r="AF3" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="H3" t="s">
+      <c r="AG3" t="s">
         <v>116</v>
       </c>
-      <c r="I3" t="s">
+      <c r="AH3" t="s">
         <v>116</v>
       </c>
-      <c r="J3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>116</v>
-      </c>
-      <c r="M3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N3" t="s">
-        <v>116</v>
-      </c>
-      <c r="O3" t="s">
-        <v>116</v>
-      </c>
-      <c r="P3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>116</v>
-      </c>
-      <c r="R3" t="s">
-        <v>116</v>
-      </c>
-      <c r="S3" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" t="s">
-        <v>116</v>
-      </c>
-      <c r="U3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" t="s">
-        <v>116</v>
-      </c>
-      <c r="W3" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" t="s">
+      <c r="AK3" t="s">
         <v>117</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AL3" t="s">
         <v>117</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AM3" t="s">
         <v>117</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AN3" t="s">
         <v>117</v>
       </c>
-      <c r="AE3" s="10" t="s">
+      <c r="AO3" t="s">
         <v>117</v>
       </c>
-      <c r="AF3" s="24" t="s">
+      <c r="AP3" t="s">
         <v>117</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AQ3" t="s">
         <v>117</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AR3" t="s">
         <v>117</v>
       </c>
-      <c r="AK3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>118</v>
-      </c>
       <c r="AS3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AT3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AU3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AV3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AW3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AX3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AY3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AZ3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BA3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BB3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BC3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BD3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BE3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BF3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BJ3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BK3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BL3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:64" x14ac:dyDescent="0.2">
@@ -3225,19 +3285,19 @@
         <v>1</v>
       </c>
       <c r="AA4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB4" t="s">
         <v>119</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>120</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>121</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="AE4" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -3338,19 +3398,19 @@
         <v>1</v>
       </c>
       <c r="AA5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB5" t="s">
         <v>119</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>120</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>121</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="AE5" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3451,19 +3511,19 @@
         <v>1</v>
       </c>
       <c r="AA6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB6" t="s">
         <v>119</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>120</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>121</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="AE6" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -3564,19 +3624,19 @@
         <v>0</v>
       </c>
       <c r="AA7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB7" t="s">
         <v>124</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>125</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>126</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="AE7" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="AK7">
         <v>2500</v>
@@ -3677,19 +3737,19 @@
         <v>1</v>
       </c>
       <c r="AA8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB8" t="s">
         <v>124</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AC8" t="s">
         <v>125</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>126</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="AE8" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="AK8">
         <v>2500</v>
@@ -3790,19 +3850,19 @@
         <v>1</v>
       </c>
       <c r="AA9" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB9" t="s">
         <v>124</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AC9" t="s">
         <v>125</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>126</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="AE9" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="AK9">
         <v>3500</v>
@@ -3903,19 +3963,19 @@
         <v>0</v>
       </c>
       <c r="AA10" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB10" t="s">
         <v>129</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AC10" t="s">
         <v>130</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AD10" t="s">
         <v>131</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AE10" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="AE10" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="AK10">
         <v>5000</v>
@@ -4016,19 +4076,19 @@
         <v>1</v>
       </c>
       <c r="AA11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB11" t="s">
         <v>129</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AC11" t="s">
         <v>130</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AD11" t="s">
         <v>131</v>
       </c>
-      <c r="AD11" t="s">
+      <c r="AE11" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="AE11" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="AK11">
         <v>5000</v>
@@ -4129,19 +4189,19 @@
         <v>1</v>
       </c>
       <c r="AA12" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB12" t="s">
         <v>129</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
         <v>130</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AD12" t="s">
         <v>131</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AE12" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="AE12" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="AK12">
         <v>7000</v>
@@ -4242,19 +4302,19 @@
         <v>0</v>
       </c>
       <c r="AA13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB13" t="s">
         <v>134</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
         <v>135</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AD13" t="s">
         <v>136</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AE13" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="AE13" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="AK13">
         <v>10000</v>
@@ -4355,19 +4415,19 @@
         <v>1</v>
       </c>
       <c r="AA14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB14" t="s">
         <v>134</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
         <v>135</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AD14" t="s">
         <v>136</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AE14" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="AE14" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="AK14">
         <v>10000</v>
@@ -4468,19 +4528,19 @@
         <v>1</v>
       </c>
       <c r="AA15" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB15" t="s">
         <v>134</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AC15" t="s">
         <v>135</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AD15" t="s">
         <v>136</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AE15" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="AE15" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="AK15">
         <v>14000</v>
@@ -4587,19 +4647,19 @@
         <v>0</v>
       </c>
       <c r="AA16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB16" t="s">
         <v>139</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AC16" t="s">
         <v>140</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AD16" t="s">
         <v>141</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AE16" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="AE16" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="AK16">
         <v>0</v>
@@ -4706,19 +4766,19 @@
         <v>0</v>
       </c>
       <c r="AA17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB17" t="s">
         <v>139</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AC17" t="s">
         <v>140</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AD17" t="s">
         <v>141</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AE17" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="AE17" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="AK17">
         <v>0</v>
@@ -4819,19 +4879,19 @@
         <v>1</v>
       </c>
       <c r="AA18" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB18" t="s">
         <v>144</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AC18" t="s">
         <v>145</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AD18" t="s">
         <v>146</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AE18" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="AE18" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="AK18">
         <v>10000</v>
@@ -4932,19 +4992,19 @@
         <v>1</v>
       </c>
       <c r="AA19" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB19" t="s">
         <v>144</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AC19" t="s">
         <v>145</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AD19" t="s">
         <v>146</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AE19" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="AE19" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="AK19">
         <v>14000</v>
@@ -5045,19 +5105,19 @@
         <v>1</v>
       </c>
       <c r="AA20" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB20" t="s">
         <v>119</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AC20" t="s">
         <v>120</v>
       </c>
-      <c r="AC20" t="s">
+      <c r="AD20" t="s">
         <v>121</v>
       </c>
-      <c r="AD20" t="s">
+      <c r="AE20" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="AE20" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="AK20">
         <v>0</v>
@@ -5158,19 +5218,19 @@
         <v>1</v>
       </c>
       <c r="AA21" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB21" t="s">
         <v>119</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AC21" t="s">
         <v>120</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AD21" t="s">
         <v>121</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AE21" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="AE21" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="AK21">
         <v>0</v>
@@ -5271,19 +5331,19 @@
         <v>1</v>
       </c>
       <c r="AA22" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB22" t="s">
         <v>124</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AC22" t="s">
         <v>125</v>
       </c>
-      <c r="AC22" t="s">
+      <c r="AD22" t="s">
         <v>126</v>
       </c>
-      <c r="AD22" t="s">
+      <c r="AE22" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="AE22" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="AK22">
         <v>2500</v>
@@ -5384,19 +5444,19 @@
         <v>1</v>
       </c>
       <c r="AA23" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB23" t="s">
         <v>124</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AC23" t="s">
         <v>125</v>
       </c>
-      <c r="AC23" t="s">
+      <c r="AD23" t="s">
         <v>126</v>
       </c>
-      <c r="AD23" t="s">
+      <c r="AE23" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="AE23" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="AK23">
         <v>3500</v>
@@ -5497,19 +5557,19 @@
         <v>1</v>
       </c>
       <c r="AA24" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB24" t="s">
         <v>129</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AC24" t="s">
         <v>130</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AD24" t="s">
         <v>131</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AE24" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="AE24" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="AK24">
         <v>5000</v>
@@ -5610,19 +5670,19 @@
         <v>1</v>
       </c>
       <c r="AA25" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB25" t="s">
         <v>129</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AC25" t="s">
         <v>130</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AD25" t="s">
         <v>131</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="AE25" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="AE25" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="AK25">
         <v>7000</v>
@@ -5723,19 +5783,19 @@
         <v>1</v>
       </c>
       <c r="AA26" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB26" t="s">
         <v>134</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AC26" t="s">
         <v>135</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AD26" t="s">
         <v>136</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AE26" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="AE26" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="AK26">
         <v>10000</v>
@@ -5836,19 +5896,19 @@
         <v>1</v>
       </c>
       <c r="AA27" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB27" t="s">
         <v>134</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AC27" t="s">
         <v>135</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AD27" t="s">
         <v>136</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AE27" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="AE27" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="AK27">
         <v>14000</v>
@@ -5949,19 +6009,19 @@
         <v>1</v>
       </c>
       <c r="AA28" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB28" t="s">
         <v>144</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AC28" t="s">
         <v>145</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AD28" t="s">
         <v>146</v>
       </c>
-      <c r="AD28" t="s">
+      <c r="AE28" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="AE28" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="AK28">
         <v>10000</v>
@@ -6062,19 +6122,19 @@
         <v>1</v>
       </c>
       <c r="AA29" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB29" t="s">
         <v>144</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AC29" t="s">
         <v>145</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AD29" t="s">
         <v>146</v>
       </c>
-      <c r="AD29" t="s">
+      <c r="AE29" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="AE29" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="AK29">
         <v>14000</v>
@@ -6154,7 +6214,7 @@
     </row>
     <row r="30" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -6178,19 +6238,19 @@
         <v>0</v>
       </c>
       <c r="AA30" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB30" t="s">
         <v>150</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AC30" t="s">
         <v>151</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AD30" t="s">
         <v>152</v>
       </c>
-      <c r="AD30" t="s">
+      <c r="AE30" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="AE30" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="AK30">
         <v>0</v>
@@ -6270,7 +6330,7 @@
     </row>
     <row r="31" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -6294,19 +6354,19 @@
         <v>0</v>
       </c>
       <c r="AA31" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB31" t="s">
         <v>150</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AC31" t="s">
         <v>151</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AD31" t="s">
         <v>152</v>
       </c>
-      <c r="AD31" t="s">
+      <c r="AE31" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="AE31" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="AK31">
         <v>0</v>
@@ -6386,7 +6446,7 @@
     </row>
     <row r="32" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B32">
         <v>31</v>
@@ -6410,19 +6470,19 @@
         <v>0</v>
       </c>
       <c r="AA32" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB32" t="s">
         <v>150</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AC32" t="s">
         <v>151</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AD32" t="s">
         <v>152</v>
       </c>
-      <c r="AD32" t="s">
+      <c r="AE32" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="AE32" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="AK32">
         <v>0</v>
@@ -6502,7 +6562,7 @@
     </row>
     <row r="33" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B33">
         <v>32</v>
@@ -6526,19 +6586,19 @@
         <v>0</v>
       </c>
       <c r="AA33" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB33" t="s">
         <v>150</v>
       </c>
-      <c r="AB33" t="s">
+      <c r="AC33" t="s">
         <v>151</v>
       </c>
-      <c r="AC33" t="s">
+      <c r="AD33" t="s">
         <v>152</v>
       </c>
-      <c r="AD33" t="s">
+      <c r="AE33" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="AE33" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="AK33">
         <v>0</v>
@@ -6618,7 +6678,7 @@
     </row>
     <row r="34" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B34">
         <v>33</v>
@@ -6648,28 +6708,28 @@
         <v>1</v>
       </c>
       <c r="AA34" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB34" t="s">
         <v>155</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AC34" t="s">
         <v>156</v>
       </c>
-      <c r="AC34" t="s">
+      <c r="AD34" t="s">
         <v>157</v>
       </c>
-      <c r="AD34" t="s">
+      <c r="AE34" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="AE34" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="AF34" s="26">
         <v>3651</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AK34">
         <v>5000</v>
@@ -6749,7 +6809,7 @@
     </row>
     <row r="35" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B35">
         <v>34</v>
@@ -6779,19 +6839,19 @@
         <v>1</v>
       </c>
       <c r="AA35" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>159</v>
+      </c>
+      <c r="AC35" t="s">
         <v>160</v>
       </c>
-      <c r="AB35" t="s">
-        <v>160</v>
-      </c>
-      <c r="AC35" t="s">
+      <c r="AD35" t="s">
         <v>161</v>
       </c>
-      <c r="AD35" t="s">
+      <c r="AE35" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="AE35" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="AK35">
         <v>5000</v>
@@ -6871,7 +6931,7 @@
     </row>
     <row r="36" spans="1:64" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B36">
         <v>35</v>
@@ -6904,31 +6964,31 @@
         <v>1</v>
       </c>
       <c r="AA36" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB36" t="s">
         <v>164</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AC36" t="s">
         <v>165</v>
       </c>
-      <c r="AC36" t="s">
+      <c r="AD36" t="s">
         <v>166</v>
       </c>
-      <c r="AD36" t="s">
+      <c r="AE36" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="AE36" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="AF36" s="35">
         <v>20422</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AH36" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="AI36" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="AI36" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="AK36">
         <v>5000</v>
@@ -7032,19 +7092,19 @@
         <v>1</v>
       </c>
       <c r="AA37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB37" t="s">
         <v>169</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AC37" t="s">
         <v>170</v>
       </c>
-      <c r="AC37" t="s">
+      <c r="AD37" t="s">
         <v>171</v>
       </c>
-      <c r="AD37" t="s">
+      <c r="AE37" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="AE37" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="AK37">
         <v>1500</v>
@@ -7157,10 +7217,10 @@
         <v>1</v>
       </c>
       <c r="AA38" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB38" t="s">
         <v>174</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>175</v>
       </c>
       <c r="AE38" s="10"/>
       <c r="AK38">
@@ -7274,10 +7334,10 @@
         <v>1</v>
       </c>
       <c r="AA39" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB39" t="s">
         <v>174</v>
-      </c>
-      <c r="AB39" t="s">
-        <v>175</v>
       </c>
       <c r="AE39" s="10"/>
       <c r="AK39">
@@ -7391,10 +7451,10 @@
         <v>1</v>
       </c>
       <c r="AA40" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB40" t="s">
         <v>174</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>175</v>
       </c>
       <c r="AE40" s="10"/>
       <c r="AK40">
@@ -7484,7 +7544,7 @@
     </row>
     <row r="41" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -7517,28 +7577,28 @@
         <v>1</v>
       </c>
       <c r="AA41" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB41" t="s">
         <v>176</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AC41" t="s">
         <v>177</v>
       </c>
-      <c r="AC41" t="s">
+      <c r="AD41" t="s">
         <v>178</v>
       </c>
-      <c r="AD41" t="s">
+      <c r="AE41" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="AE41" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="AF41" s="26">
         <v>3390</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AK41">
         <v>5000</v>
@@ -7618,7 +7678,7 @@
     </row>
     <row r="42" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B42">
         <v>41</v>
@@ -7651,31 +7711,31 @@
         <v>1</v>
       </c>
       <c r="AA42" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB42" t="s">
         <v>181</v>
       </c>
-      <c r="AB42" t="s">
+      <c r="AC42" t="s">
         <v>182</v>
       </c>
-      <c r="AC42" t="s">
+      <c r="AD42" t="s">
         <v>183</v>
       </c>
-      <c r="AD42" t="s">
+      <c r="AE42" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="AE42" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="AF42" s="26">
         <v>3650</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AK42">
         <v>5000</v>
@@ -7755,7 +7815,7 @@
     </row>
     <row r="43" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B43">
         <v>42</v>
@@ -7782,19 +7842,19 @@
         <v>1</v>
       </c>
       <c r="AA43" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB43" t="s">
         <v>187</v>
       </c>
-      <c r="AB43" t="s">
+      <c r="AC43" t="s">
         <v>188</v>
       </c>
-      <c r="AC43" t="s">
+      <c r="AD43" t="s">
         <v>189</v>
       </c>
-      <c r="AD43" t="s">
+      <c r="AE43" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="AE43" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="AK43">
         <v>0</v>
@@ -7874,7 +7934,7 @@
     </row>
     <row r="44" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B44">
         <v>43</v>
@@ -7901,19 +7961,19 @@
         <v>1</v>
       </c>
       <c r="AA44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB44" t="s">
         <v>187</v>
       </c>
-      <c r="AB44" t="s">
+      <c r="AC44" t="s">
         <v>188</v>
       </c>
-      <c r="AC44" t="s">
+      <c r="AD44" t="s">
         <v>189</v>
       </c>
-      <c r="AD44" t="s">
+      <c r="AE44" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="AE44" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="AK44">
         <v>5000</v>
@@ -7993,7 +8053,7 @@
     </row>
     <row r="45" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B45">
         <v>44</v>
@@ -8023,19 +8083,19 @@
         <v>1</v>
       </c>
       <c r="AA45" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB45" t="s">
         <v>194</v>
       </c>
-      <c r="AB45" t="s">
+      <c r="AC45" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="AC45" s="11" t="s">
+      <c r="AD45" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="AD45" s="12" t="s">
+      <c r="AE45" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="AE45" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="AK45">
         <v>5000</v>
@@ -8115,7 +8175,7 @@
     </row>
     <row r="46" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B46">
         <v>45</v>
@@ -8145,31 +8205,31 @@
         <v>1</v>
       </c>
       <c r="AA46" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB46" t="s">
         <v>200</v>
       </c>
-      <c r="AB46" t="s">
+      <c r="AC46" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="AC46" s="11" t="s">
+      <c r="AD46" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="AD46" s="12" t="s">
+      <c r="AE46" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="AE46" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="AF46" s="26">
         <v>3528</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AK46">
         <v>5000</v>
@@ -8249,7 +8309,7 @@
     </row>
     <row r="47" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B47">
         <v>46</v>
@@ -8279,28 +8339,28 @@
         <v>1</v>
       </c>
       <c r="AA47" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB47" t="s">
         <v>206</v>
       </c>
-      <c r="AB47" t="s">
+      <c r="AC47" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="AC47" s="13" t="s">
+      <c r="AD47" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="AD47" s="14" t="s">
+      <c r="AE47" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="AE47" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="AF47" s="26">
         <v>3588</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AI47" s="2"/>
       <c r="AK47">
@@ -8381,7 +8441,7 @@
     </row>
     <row r="48" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B48">
         <v>47</v>
@@ -8411,28 +8471,28 @@
         <v>1</v>
       </c>
       <c r="AA48" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB48" t="s">
         <v>211</v>
       </c>
-      <c r="AB48" t="s">
+      <c r="AC48" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="AC48" s="15" t="s">
+      <c r="AD48" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="AD48" s="15" t="s">
+      <c r="AE48" s="15" t="s">
         <v>214</v>
-      </c>
-      <c r="AE48" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="AF48" s="27">
         <v>3705</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AI48" s="2"/>
       <c r="AK48">
@@ -8513,7 +8573,7 @@
     </row>
     <row r="49" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B49">
         <v>48</v>
@@ -8543,31 +8603,31 @@
         <v>1</v>
       </c>
       <c r="AA49" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB49" t="s">
         <v>216</v>
       </c>
-      <c r="AB49" t="s">
+      <c r="AC49" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="AC49" s="16" t="s">
+      <c r="AD49" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="AD49" s="17" t="s">
+      <c r="AE49" s="17" t="s">
         <v>219</v>
-      </c>
-      <c r="AE49" s="17" t="s">
-        <v>220</v>
       </c>
       <c r="AF49" s="27">
         <v>3857</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AH49" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="AI49" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="AI49" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="AK49">
         <v>5000</v>
@@ -8647,7 +8707,7 @@
     </row>
     <row r="50" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B50">
         <v>49</v>
@@ -8677,31 +8737,31 @@
         <v>1</v>
       </c>
       <c r="AA50" t="s">
+        <v>220</v>
+      </c>
+      <c r="AB50" t="s">
         <v>221</v>
       </c>
-      <c r="AB50" t="s">
+      <c r="AC50" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="AC50" s="18" t="s">
+      <c r="AD50" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="AD50" s="15" t="s">
+      <c r="AE50" s="15" t="s">
         <v>224</v>
-      </c>
-      <c r="AE50" s="15" t="s">
-        <v>225</v>
       </c>
       <c r="AF50" s="27">
         <v>3987</v>
       </c>
       <c r="AG50" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AH50" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="AI50" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="AI50" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="AK50">
         <v>5000</v>
@@ -8781,7 +8841,7 @@
     </row>
     <row r="51" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -8811,31 +8871,31 @@
         <v>1</v>
       </c>
       <c r="AA51" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="AB51" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="AB51" s="8" t="s">
+      <c r="AC51" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="AC51" s="19" t="s">
+      <c r="AD51" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="AD51" s="20" t="s">
+      <c r="AE51" s="21" t="s">
         <v>229</v>
-      </c>
-      <c r="AE51" s="21" t="s">
-        <v>230</v>
       </c>
       <c r="AF51" s="26">
         <v>4208</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AH51" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="AI51" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="AI51" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="AK51">
         <v>5000</v>
@@ -8915,7 +8975,7 @@
     </row>
     <row r="52" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B52">
         <v>51</v>
@@ -8948,31 +9008,31 @@
         <v>1</v>
       </c>
       <c r="AA52" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="AB52" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="AB52" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="AC52" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="AD52" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="AD52" s="21" t="s">
+      <c r="AE52" s="21" t="s">
         <v>472</v>
-      </c>
-      <c r="AE52" s="21" t="s">
-        <v>473</v>
       </c>
       <c r="AF52" s="35">
         <v>20194</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH52" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="AI52" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="AI52" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="AK52">
         <v>5000</v>
@@ -9052,7 +9112,7 @@
     </row>
     <row r="53" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B53">
         <v>52</v>
@@ -9082,19 +9142,19 @@
         <v>1</v>
       </c>
       <c r="AA53" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="AB53" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="AB53" s="2" t="s">
-        <v>503</v>
-      </c>
       <c r="AC53" s="37" t="s">
+        <v>506</v>
+      </c>
+      <c r="AD53" s="38" t="s">
         <v>507</v>
       </c>
-      <c r="AD53" s="38" t="s">
+      <c r="AE53" s="38" t="s">
         <v>508</v>
-      </c>
-      <c r="AE53" s="38" t="s">
-        <v>509</v>
       </c>
       <c r="AK53">
         <v>5000</v>
@@ -9174,7 +9234,7 @@
     </row>
     <row r="54" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B54">
         <v>53</v>
@@ -9204,28 +9264,28 @@
         <v>1</v>
       </c>
       <c r="AA54" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AB54" s="2" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="AC54" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AD54" s="50" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE54" s="50" t="s">
         <v>518</v>
-      </c>
-      <c r="AE54" s="50" t="s">
-        <v>519</v>
       </c>
       <c r="AF54" s="25">
         <v>25101013</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AK54">
         <v>5000</v>
@@ -9361,6 +9421,7 @@
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9378,70 +9439,70 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E1" t="s">
         <v>232</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>233</v>
-      </c>
-      <c r="F1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" t="s">
         <v>235</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>236</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>237</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>238</v>
-      </c>
-      <c r="F2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
         <v>115</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" t="s">
         <v>116</v>
       </c>
-      <c r="C3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
-      </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" t="s">
         <v>240</v>
-      </c>
-      <c r="D4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -9455,7 +9516,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -9472,7 +9533,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -9489,7 +9550,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -9506,7 +9567,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -9523,7 +9584,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9540,7 +9601,7 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -9557,7 +9618,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -9574,7 +9635,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F12">
         <v>8</v>
@@ -9591,7 +9652,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F13">
         <v>9</v>
@@ -9608,7 +9669,7 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -9625,7 +9686,7 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F15">
         <v>11</v>
@@ -9642,7 +9703,7 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F16">
         <v>12</v>
@@ -9659,7 +9720,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F17">
         <v>13</v>
@@ -9676,7 +9737,7 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F18">
         <v>14</v>
@@ -9693,7 +9754,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F19">
         <v>15</v>
@@ -9726,104 +9787,104 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
       </c>
       <c r="C1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1" t="s">
         <v>257</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>258</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>259</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>260</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>261</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>262</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>263</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>264</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>265</v>
-      </c>
-      <c r="L1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" t="s">
         <v>267</v>
       </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
         <v>268</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>269</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>270</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>271</v>
-      </c>
-      <c r="L2" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
         <v>115</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
         <v>116</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>116</v>
       </c>
-      <c r="D3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
-      </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -9834,22 +9895,22 @@
         <v>1000</v>
       </c>
       <c r="D4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" t="s">
         <v>277</v>
-      </c>
-      <c r="I4" t="s">
-        <v>278</v>
       </c>
       <c r="J4">
         <v>10000</v>
@@ -9869,22 +9930,22 @@
         <v>1000</v>
       </c>
       <c r="D5" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" t="s">
         <v>279</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" t="s">
         <v>283</v>
-      </c>
-      <c r="I5" t="s">
-        <v>284</v>
       </c>
       <c r="J5">
         <v>10001</v>
@@ -9904,22 +9965,22 @@
         <v>1000</v>
       </c>
       <c r="D6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E6" t="s">
         <v>285</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" t="s">
         <v>289</v>
-      </c>
-      <c r="I6" t="s">
-        <v>290</v>
       </c>
       <c r="J6">
         <v>10002</v>
@@ -9939,22 +10000,22 @@
         <v>1000</v>
       </c>
       <c r="D7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E7" t="s">
         <v>291</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" t="s">
         <v>295</v>
-      </c>
-      <c r="I7" t="s">
-        <v>296</v>
       </c>
       <c r="J7">
         <v>10003</v>
@@ -9974,22 +10035,22 @@
         <v>1000</v>
       </c>
       <c r="D8" t="s">
+        <v>296</v>
+      </c>
+      <c r="E8" t="s">
         <v>297</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" t="s">
         <v>301</v>
-      </c>
-      <c r="I8" t="s">
-        <v>302</v>
       </c>
       <c r="J8">
         <v>10004</v>
@@ -10020,37 +10081,37 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
         <v>117</v>
-      </c>
-      <c r="C3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" t="s">
         <v>304</v>
-      </c>
-      <c r="B4" t="s">
-        <v>305</v>
       </c>
       <c r="C4">
         <v>1000</v>
@@ -10058,10 +10119,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" t="s">
         <v>306</v>
-      </c>
-      <c r="B5" t="s">
-        <v>307</v>
       </c>
       <c r="C5">
         <v>303991</v>
@@ -10091,91 +10152,91 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
       </c>
       <c r="C1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>308</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="22" t="s">
         <v>309</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H1" t="s">
         <v>311</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>312</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>313</v>
-      </c>
-      <c r="J1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" t="s">
         <v>315</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="E2" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="F2" s="22" t="s">
         <v>318</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="G2" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="H2" t="s">
         <v>319</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="H2" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
         <v>115</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>116</v>
       </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
       <c r="D3" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="24" t="s">
-        <v>117</v>
-      </c>
       <c r="F3" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G3" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" t="s">
         <v>116</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -10194,12 +10255,12 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -10218,18 +10279,18 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D6" s="27">
         <v>3</v>
@@ -10244,18 +10305,18 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D7" s="27">
         <v>4</v>
@@ -10272,13 +10333,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D8" s="27">
         <v>5</v>
@@ -10293,21 +10354,21 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D9" s="27">
         <v>6</v>
@@ -10322,21 +10383,21 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D10" s="27">
         <v>7</v>
@@ -10351,18 +10412,18 @@
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B11">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D11" s="27">
         <v>8</v>
@@ -10377,19 +10438,19 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B12">
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D12" s="27">
         <v>9</v>
@@ -10404,19 +10465,19 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B13">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D13" s="27">
         <v>10</v>
@@ -10431,21 +10492,21 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B14">
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D14" s="27">
         <v>11</v>
@@ -10460,21 +10521,21 @@
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B15">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D15" s="27">
         <v>12</v>
@@ -10489,21 +10550,21 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B16">
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D16" s="34">
         <v>13</v>
@@ -10518,21 +10579,21 @@
         <v>1</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B17">
         <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D17" s="34">
         <v>14</v>
@@ -10547,21 +10608,21 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B18">
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D18" s="25">
         <v>15</v>
@@ -10576,18 +10637,18 @@
         <v>1</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="46" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B19" s="47">
         <v>16</v>
       </c>
       <c r="C19" s="46" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D19" s="48">
         <v>16</v>
@@ -10602,7 +10663,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="46" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I19" s="47"/>
     </row>
@@ -10631,316 +10692,316 @@
   <sheetData>
     <row r="1" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E1" t="s">
         <v>365</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>366</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>367</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>368</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>369</v>
       </c>
-      <c r="I1" t="s">
-        <v>370</v>
-      </c>
       <c r="J1" t="s">
+        <v>408</v>
+      </c>
+      <c r="K1" t="s">
         <v>409</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>410</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>411</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>412</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>413</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>414</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>415</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>416</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>417</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>418</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>419</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>420</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>421</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>422</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>423</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>424</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>425</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>426</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>427</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>428</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>429</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>430</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>431</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>432</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>433</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>434</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>435</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>436</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>437</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>438</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>439</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>440</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>441</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>442</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>443</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>444</v>
       </c>
-      <c r="AT1" t="s">
-        <v>445</v>
-      </c>
       <c r="AU1" t="s">
+        <v>457</v>
+      </c>
+      <c r="AV1" t="s">
         <v>458</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>459</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:49" ht="68.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D2" s="29" t="s">
+        <v>378</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>379</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="F2" s="29" t="s">
         <v>380</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="G2" s="29" t="s">
         <v>381</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="H2" s="29" t="s">
         <v>382</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="I2" s="29" t="s">
         <v>383</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="J2" s="29" t="s">
         <v>384</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="K2" s="29" t="s">
         <v>385</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="L2" s="29" t="s">
         <v>386</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="M2" s="29" t="s">
         <v>387</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="N2" s="29" t="s">
         <v>388</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="O2" s="29" t="s">
         <v>389</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="P2" s="29" t="s">
         <v>390</v>
       </c>
-      <c r="P2" s="29" t="s">
+      <c r="Q2" s="29" t="s">
         <v>391</v>
       </c>
-      <c r="Q2" s="29" t="s">
+      <c r="R2" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="R2" s="29" t="s">
+      <c r="S2" s="29" t="s">
         <v>393</v>
       </c>
-      <c r="S2" s="29" t="s">
+      <c r="T2" s="29" t="s">
         <v>394</v>
       </c>
-      <c r="T2" s="29" t="s">
+      <c r="U2" s="29" t="s">
         <v>395</v>
       </c>
-      <c r="U2" s="29" t="s">
+      <c r="V2" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="V2" s="29" t="s">
+      <c r="W2" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="W2" s="29" t="s">
+      <c r="X2" s="29" t="s">
         <v>398</v>
       </c>
-      <c r="X2" s="29" t="s">
+      <c r="Y2" s="29" t="s">
         <v>399</v>
       </c>
-      <c r="Y2" s="29" t="s">
+      <c r="Z2" s="29" t="s">
         <v>400</v>
       </c>
-      <c r="Z2" s="29" t="s">
+      <c r="AA2" s="29" t="s">
         <v>401</v>
       </c>
-      <c r="AA2" s="29" t="s">
+      <c r="AB2" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="AB2" s="29" t="s">
+      <c r="AC2" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="AD2" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="AE2" s="29" t="s">
         <v>403</v>
       </c>
-      <c r="AC2" s="31" t="s">
-        <v>453</v>
-      </c>
-      <c r="AD2" s="31" t="s">
+      <c r="AF2" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="AE2" s="29" t="s">
+      <c r="AG2" s="29" t="s">
         <v>404</v>
       </c>
-      <c r="AF2" s="31" t="s">
+      <c r="AH2" s="31" t="s">
         <v>455</v>
       </c>
-      <c r="AG2" s="29" t="s">
+      <c r="AI2" s="29" t="s">
         <v>405</v>
       </c>
-      <c r="AH2" s="31" t="s">
+      <c r="AJ2" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="AK2" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="AL2" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="AM2" s="32" t="s">
+        <v>447</v>
+      </c>
+      <c r="AN2" s="29" t="s">
+        <v>407</v>
+      </c>
+      <c r="AO2" s="31" t="s">
         <v>456</v>
       </c>
-      <c r="AI2" s="29" t="s">
-        <v>406</v>
-      </c>
-      <c r="AJ2" s="29" t="s">
-        <v>407</v>
-      </c>
-      <c r="AK2" s="32" t="s">
-        <v>447</v>
-      </c>
-      <c r="AL2" s="31" t="s">
-        <v>446</v>
-      </c>
-      <c r="AM2" s="32" t="s">
+      <c r="AP2" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="AN2" s="29" t="s">
-        <v>408</v>
-      </c>
-      <c r="AO2" s="31" t="s">
-        <v>457</v>
-      </c>
-      <c r="AP2" s="33" t="s">
+      <c r="AQ2" s="31" t="s">
+        <v>451</v>
+      </c>
+      <c r="AR2" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="AQ2" s="31" t="s">
-        <v>452</v>
-      </c>
-      <c r="AR2" s="31" t="s">
+      <c r="AS2" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="AS2" s="31" t="s">
-        <v>451</v>
-      </c>
       <c r="AT2" s="31" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AU2" t="s">
+        <v>460</v>
+      </c>
+      <c r="AV2" t="s">
         <v>461</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>462</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
         <v>115</v>
       </c>
-      <c r="B3" t="s">
-        <v>116</v>
-      </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:49" s="40" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B4" s="40">
         <v>1</v>
@@ -11089,7 +11150,7 @@
     </row>
     <row r="5" spans="1:49" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -11238,7 +11299,7 @@
     </row>
     <row r="6" spans="1:49" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -11387,7 +11448,7 @@
     </row>
     <row r="7" spans="1:49" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -11536,7 +11597,7 @@
     </row>
     <row r="8" spans="1:49" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -11685,7 +11746,7 @@
     </row>
     <row r="9" spans="1:49" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -11834,7 +11895,7 @@
     </row>
     <row r="10" spans="1:49" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -11983,7 +12044,7 @@
     </row>
     <row r="11" spans="1:49" s="40" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B11" s="40">
         <v>101</v>
@@ -12569,13 +12630,13 @@
   <sheetData>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
@@ -12583,13 +12644,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>322</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
@@ -12597,13 +12658,13 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
@@ -12611,13 +12672,13 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
@@ -12625,13 +12686,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
@@ -12639,13 +12700,13 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
@@ -12653,7 +12714,7 @@
         <v>6</v>
       </c>
       <c r="G10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
@@ -12661,7 +12722,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
@@ -12669,37 +12730,37 @@
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/desktop.xlsx
+++ b/source/bin/excel/desktop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3049BE-A7F8-4FEB-BF8B-463AFAC7F3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8186C5F5-D0E7-4929-ACFC-41038AA52F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
             <charset val="134"/>
             <scheme val="minor"/>
           </rPr>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="527">
   <si>
     <t>sheet</t>
   </si>
@@ -1611,23 +1612,46 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>tbd</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>強奪之戰</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>qiangduozhizhan</t>
     <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/activity_banner/rotationalmatch/qiangduozhizhan.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/room_rule/qiangduozhizhan1.png</t>
+  </si>
+  <si>
+    <t>myres2/room_rule/qiangduozhizhan1.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/room_rule/qiangduozhizhan2.png</t>
+  </si>
+  <si>
+    <t>myres2/room_rule/qiangduozhizhan2.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>強奪の戦</t>
+  </si>
+  <si>
+    <t>Vulture's Deal</t>
+  </si>
+  <si>
+    <t>쟁탈전</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1760,6 +1784,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1918,7 +1950,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2049,6 +2081,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -9222,25 +9257,28 @@
         <v>515</v>
       </c>
       <c r="AC55" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="AD55" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="AE55" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="AF55" s="2" t="s">
-        <v>517</v>
+      <c r="AD55" s="52" t="s">
+        <v>524</v>
+      </c>
+      <c r="AE55" s="52" t="s">
+        <v>525</v>
+      </c>
+      <c r="AF55" s="52" t="s">
+        <v>526</v>
       </c>
       <c r="AG55" s="25">
-        <v>25101013</v>
+        <v>26041085</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>289</v>
+        <v>519</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>290</v>
+        <v>520</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>522</v>
       </c>
       <c r="AL55">
         <v>5000</v>
@@ -10630,24 +10668,26 @@
         <v>17</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D20" s="48">
         <v>17</v>
       </c>
       <c r="E20" s="49">
-        <v>25101012</v>
+        <v>26041083</v>
       </c>
       <c r="F20" s="49">
-        <v>25101014</v>
+        <v>26041086</v>
       </c>
       <c r="G20" s="48">
         <v>1</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>290</v>
-      </c>
-      <c r="I20" s="47"/>
+        <v>521</v>
+      </c>
+      <c r="I20" s="46" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C23" s="2"/>

--- a/source/bin/excel/desktop.xlsx
+++ b/source/bin/excel/desktop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8186C5F5-D0E7-4929-ACFC-41038AA52F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B63C23-1EDE-463D-83A9-93E088F33F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="532">
   <si>
     <t>sheet</t>
   </si>
@@ -719,9 +719,6 @@
     <t>RPG用匹配</t>
   </si>
   <si>
-    <t>三透牌</t>
-  </si>
-  <si>
     <t>明镜之战</t>
   </si>
   <si>
@@ -735,9 +732,6 @@
   </si>
   <si>
     <t>명경전</t>
-  </si>
-  <si>
-    <t>暗牌</t>
   </si>
   <si>
     <t>暗夜之战</t>
@@ -1645,6 +1639,34 @@
   </si>
   <si>
     <t>쟁탈전</t>
+  </si>
+  <si>
+    <t>明镜之战</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗夜之战</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/activity_banner/rotationalmatch/mingjing.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/room_rule/mingjing.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/room_rule/xiakeshang.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/room_rule/beishui.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>myres2/activity_banner/rotationalmatch/beishui.png</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1950,7 +1972,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2084,13 +2106,24 @@
     <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="常规 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2645,7 +2678,7 @@
         <v>37</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="Y1" t="s">
         <v>38</v>
@@ -2842,7 +2875,7 @@
         <v>100</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Y2" t="s">
         <v>101</v>
@@ -7911,8 +7944,8 @@
       </c>
     </row>
     <row r="45" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>220</v>
+      <c r="A45" s="53" t="s">
+        <v>525</v>
       </c>
       <c r="B45">
         <v>44</v>
@@ -7926,8 +7959,8 @@
       <c r="E45">
         <v>2</v>
       </c>
-      <c r="F45">
-        <v>1226</v>
+      <c r="F45" s="51">
+        <v>260650</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -7942,19 +7975,28 @@
         <v>1</v>
       </c>
       <c r="AB45" t="s">
+        <v>220</v>
+      </c>
+      <c r="AC45" t="s">
         <v>221</v>
       </c>
-      <c r="AC45" t="s">
+      <c r="AD45" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="AD45" s="11" t="s">
+      <c r="AE45" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="AE45" s="12" t="s">
+      <c r="AF45" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="AF45" s="10" t="s">
-        <v>225</v>
+      <c r="AG45" s="26">
+        <v>3527</v>
+      </c>
+      <c r="AH45" s="53" t="s">
+        <v>527</v>
+      </c>
+      <c r="AI45" s="2" t="s">
+        <v>528</v>
       </c>
       <c r="AL45">
         <v>5000</v>
@@ -8033,8 +8075,8 @@
       </c>
     </row>
     <row r="46" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>226</v>
+      <c r="A46" s="53" t="s">
+        <v>526</v>
       </c>
       <c r="B46">
         <v>45</v>
@@ -8048,8 +8090,8 @@
       <c r="E46">
         <v>2</v>
       </c>
-      <c r="F46">
-        <v>1001</v>
+      <c r="F46" s="51">
+        <v>260651</v>
       </c>
       <c r="O46">
         <v>1</v>
@@ -8064,31 +8106,31 @@
         <v>1</v>
       </c>
       <c r="AB46" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD46" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="AC46" t="s">
+      <c r="AE46" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="AD46" s="11" t="s">
+      <c r="AF46" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="AE46" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="AF46" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="AG46" s="26">
         <v>3528</v>
       </c>
-      <c r="AH46" s="2" t="s">
+      <c r="AH46" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI46" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="AJ46" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="AI46" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="AJ46" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="AL46">
         <v>5000</v>
@@ -8168,7 +8210,7 @@
     </row>
     <row r="47" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B47">
         <v>46</v>
@@ -8198,28 +8240,28 @@
         <v>1</v>
       </c>
       <c r="AB47" t="s">
+        <v>234</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD47" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="AC47" t="s">
+      <c r="AE47" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="AD47" s="13" t="s">
+      <c r="AF47" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="AE47" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="AF47" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="AG47" s="26">
         <v>3588</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AJ47" s="2"/>
       <c r="AL47">
@@ -8300,7 +8342,7 @@
     </row>
     <row r="48" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B48">
         <v>47</v>
@@ -8330,28 +8372,28 @@
         <v>1</v>
       </c>
       <c r="AB48" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>242</v>
+      </c>
+      <c r="AD48" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="AC48" t="s">
+      <c r="AE48" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="AD48" s="15" t="s">
+      <c r="AF48" s="15" t="s">
         <v>245</v>
-      </c>
-      <c r="AE48" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="AF48" s="15" t="s">
-        <v>247</v>
       </c>
       <c r="AG48" s="27">
         <v>3705</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AJ48" s="2"/>
       <c r="AL48">
@@ -8432,7 +8474,7 @@
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B49">
         <v>48</v>
@@ -8462,31 +8504,31 @@
         <v>1</v>
       </c>
       <c r="AB49" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>249</v>
+      </c>
+      <c r="AD49" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="AC49" t="s">
+      <c r="AE49" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="AD49" s="16" t="s">
+      <c r="AF49" s="17" t="s">
         <v>252</v>
-      </c>
-      <c r="AE49" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="AF49" s="17" t="s">
-        <v>254</v>
       </c>
       <c r="AG49" s="27">
         <v>3857</v>
       </c>
       <c r="AH49" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI49" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ49" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="AI49" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="AJ49" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="AL49">
         <v>5000</v>
@@ -8566,7 +8608,7 @@
     </row>
     <row r="50" spans="1:62" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B50">
         <v>49</v>
@@ -8596,31 +8638,31 @@
         <v>1</v>
       </c>
       <c r="AB50" t="s">
+        <v>256</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>257</v>
+      </c>
+      <c r="AD50" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="AC50" t="s">
+      <c r="AE50" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="AD50" s="18" t="s">
+      <c r="AF50" s="15" t="s">
         <v>260</v>
-      </c>
-      <c r="AE50" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="AF50" s="15" t="s">
-        <v>262</v>
       </c>
       <c r="AG50" s="27">
         <v>3987</v>
       </c>
       <c r="AH50" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AI50" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AJ50" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="AI50" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="AJ50" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="AL50">
         <v>5000</v>
@@ -8700,7 +8742,7 @@
     </row>
     <row r="51" spans="1:62" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -8730,31 +8772,31 @@
         <v>1</v>
       </c>
       <c r="AB51" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC51" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="AD51" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="AC51" s="8" t="s">
+      <c r="AE51" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="AD51" s="19" t="s">
+      <c r="AF51" s="21" t="s">
         <v>268</v>
-      </c>
-      <c r="AE51" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="AF51" s="21" t="s">
-        <v>270</v>
       </c>
       <c r="AG51" s="26">
         <v>4208</v>
       </c>
       <c r="AH51" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AI51" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AJ51" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="AI51" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AJ51" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="AL51">
         <v>5000</v>
@@ -8870,28 +8912,28 @@
         <v>98</v>
       </c>
       <c r="AC52" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD52" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="AE52" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="AD52" s="21" t="s">
+      <c r="AF52" s="21" t="s">
         <v>275</v>
-      </c>
-      <c r="AE52" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="AF52" s="21" t="s">
-        <v>277</v>
       </c>
       <c r="AG52" s="35">
         <v>20194</v>
       </c>
       <c r="AH52" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI52" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AJ52" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="AI52" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ52" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="AL52">
         <v>5000</v>
@@ -9004,16 +9046,25 @@
         <v>99</v>
       </c>
       <c r="AC53" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AD53" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="AE53" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="AD53" s="37" t="s">
+      <c r="AF53" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="AE53" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF53" s="38" t="s">
-        <v>284</v>
+      <c r="AG53" s="25">
+        <v>25040104</v>
+      </c>
+      <c r="AH53" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="AI53" s="2" t="s">
+        <v>530</v>
       </c>
       <c r="AL53">
         <v>5000</v>
@@ -9126,25 +9177,25 @@
         <v>100</v>
       </c>
       <c r="AC54" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AD54" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AE54" s="50" t="s">
         <v>285</v>
       </c>
-      <c r="AD54" s="2" t="s">
+      <c r="AF54" s="50" t="s">
         <v>286</v>
-      </c>
-      <c r="AE54" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="AF54" s="50" t="s">
-        <v>288</v>
       </c>
       <c r="AG54" s="25">
         <v>25101013</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>290</v>
+        <v>529</v>
       </c>
       <c r="AL54">
         <v>5000</v>
@@ -9224,7 +9275,7 @@
     </row>
     <row r="55" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B55">
         <v>54</v>
@@ -9254,31 +9305,31 @@
         <v>1</v>
       </c>
       <c r="AB55" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AC55" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="AC55" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="AD55" s="52" t="s">
+        <v>522</v>
+      </c>
+      <c r="AE55" s="52" t="s">
+        <v>523</v>
+      </c>
+      <c r="AF55" s="52" t="s">
         <v>524</v>
-      </c>
-      <c r="AE55" s="52" t="s">
-        <v>525</v>
-      </c>
-      <c r="AF55" s="52" t="s">
-        <v>526</v>
       </c>
       <c r="AG55" s="25">
         <v>26041085</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AI55" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="AJ55" t="s">
         <v>520</v>
-      </c>
-      <c r="AJ55" t="s">
-        <v>522</v>
       </c>
       <c r="AL55">
         <v>5000</v>
@@ -9409,8 +9460,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
+  <conditionalFormatting sqref="F45:F46">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9435,19 +9489,19 @@
         <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F1" t="s">
         <v>292</v>
-      </c>
-      <c r="E1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -9455,19 +9509,19 @@
         <v>79</v>
       </c>
       <c r="B2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" t="s">
         <v>295</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>296</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>297</v>
-      </c>
-      <c r="E2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -9492,10 +9546,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -9509,7 +9563,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -9526,7 +9580,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -9543,7 +9597,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -9560,7 +9614,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -9577,7 +9631,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9594,7 +9648,7 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -9611,7 +9665,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -9628,7 +9682,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F12">
         <v>8</v>
@@ -9645,7 +9699,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F13">
         <v>9</v>
@@ -9662,7 +9716,7 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -9679,7 +9733,7 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F15">
         <v>11</v>
@@ -9696,7 +9750,7 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F16">
         <v>12</v>
@@ -9713,7 +9767,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F17">
         <v>13</v>
@@ -9730,7 +9784,7 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F18">
         <v>14</v>
@@ -9747,7 +9801,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F19">
         <v>15</v>
@@ -9786,34 +9840,34 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1" t="s">
         <v>317</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>318</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>319</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>320</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>321</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>322</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>323</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>324</v>
-      </c>
-      <c r="K1" t="s">
-        <v>325</v>
-      </c>
-      <c r="L1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -9824,22 +9878,22 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I2" t="s">
         <v>327</v>
       </c>
-      <c r="D2" t="s">
+      <c r="J2" t="s">
         <v>328</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>329</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>330</v>
-      </c>
-      <c r="K2" t="s">
-        <v>331</v>
-      </c>
-      <c r="L2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -9888,22 +9942,22 @@
         <v>1000</v>
       </c>
       <c r="D4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" t="s">
         <v>336</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="I4" t="s">
-        <v>338</v>
       </c>
       <c r="J4">
         <v>10000</v>
@@ -9923,22 +9977,22 @@
         <v>1000</v>
       </c>
       <c r="D5" t="s">
+        <v>337</v>
+      </c>
+      <c r="E5" t="s">
+        <v>338</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="I5" t="s">
         <v>342</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="I5" t="s">
-        <v>344</v>
       </c>
       <c r="J5">
         <v>10001</v>
@@ -9958,22 +10012,22 @@
         <v>1000</v>
       </c>
       <c r="D6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="I6" t="s">
         <v>348</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="I6" t="s">
-        <v>350</v>
       </c>
       <c r="J6">
         <v>10002</v>
@@ -9993,22 +10047,22 @@
         <v>1000</v>
       </c>
       <c r="D7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E7" t="s">
+        <v>350</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="I7" t="s">
         <v>354</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="I7" t="s">
-        <v>356</v>
       </c>
       <c r="J7">
         <v>10003</v>
@@ -10028,22 +10082,22 @@
         <v>1000</v>
       </c>
       <c r="D8" t="s">
+        <v>355</v>
+      </c>
+      <c r="E8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="H8" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="I8" t="s">
         <v>360</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="I8" t="s">
-        <v>362</v>
       </c>
       <c r="J8">
         <v>10004</v>
@@ -10080,7 +10134,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -10101,10 +10155,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C4">
         <v>1000</v>
@@ -10112,10 +10166,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C5">
         <v>303991</v>
@@ -10151,19 +10205,19 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>368</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>369</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>370</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>46</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H1" t="s">
         <v>48</v>
@@ -10180,22 +10234,22 @@
         <v>79</v>
       </c>
       <c r="B2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>372</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" s="22" t="s">
         <v>373</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>375</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>104</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H2" t="s">
         <v>106</v>
@@ -10229,7 +10283,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -10248,12 +10302,12 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -10272,7 +10326,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -10283,7 +10337,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D6" s="27">
         <v>3</v>
@@ -10303,13 +10357,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>525</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D7" s="27">
         <v>4</v>
@@ -10323,10 +10377,13 @@
       <c r="G7" s="26">
         <v>1</v>
       </c>
+      <c r="H7" s="2" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -10347,10 +10404,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -10361,7 +10418,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D9" s="27">
         <v>6</v>
@@ -10390,7 +10447,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D10" s="27">
         <v>7</v>
@@ -10410,7 +10467,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -10431,19 +10488,19 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B12">
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D12" s="27">
         <v>9</v>
@@ -10458,19 +10515,19 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B13">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D13" s="27">
         <v>10</v>
@@ -10485,21 +10542,21 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B14">
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D14" s="27">
         <v>11</v>
@@ -10514,21 +10571,21 @@
         <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B15">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D15" s="27">
         <v>12</v>
@@ -10543,10 +10600,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -10557,7 +10614,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D16" s="34">
         <v>13</v>
@@ -10572,10 +10629,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -10586,7 +10643,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D17" s="34">
         <v>14</v>
@@ -10615,7 +10672,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D18" s="25">
         <v>15</v>
@@ -10630,7 +10687,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -10641,7 +10698,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="46" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D19" s="48">
         <v>16</v>
@@ -10656,19 +10713,19 @@
         <v>1</v>
       </c>
       <c r="H19" s="46" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I19" s="47"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B20" s="47">
         <v>17</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D20" s="48">
         <v>17</v>
@@ -10683,10 +10740,10 @@
         <v>1</v>
       </c>
       <c r="H20" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="I20" s="46" t="s">
         <v>521</v>
-      </c>
-      <c r="I20" s="46" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -10720,145 +10777,145 @@
         <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E1" t="s">
         <v>394</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>395</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>396</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>397</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>398</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>399</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>400</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>401</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>402</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>403</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>404</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>405</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>406</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>407</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>408</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>409</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>410</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>411</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>412</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>413</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>414</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>415</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>416</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>417</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>418</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>419</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>420</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>421</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>422</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>423</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>424</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>425</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>426</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>427</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>428</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>429</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>430</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>431</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>432</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>433</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>434</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>435</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>436</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>437</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>438</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>439</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="2" spans="1:49" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -10866,145 +10923,145 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>441</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="F2" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="G2" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="H2" s="29" t="s">
         <v>444</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="I2" s="29" t="s">
         <v>445</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="J2" s="29" t="s">
         <v>446</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="K2" s="29" t="s">
         <v>447</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="L2" s="29" t="s">
         <v>448</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="M2" s="29" t="s">
         <v>449</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="N2" s="29" t="s">
         <v>450</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="O2" s="29" t="s">
         <v>451</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="P2" s="29" t="s">
         <v>452</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="Q2" s="29" t="s">
         <v>453</v>
       </c>
-      <c r="P2" s="29" t="s">
+      <c r="R2" s="29" t="s">
         <v>454</v>
       </c>
-      <c r="Q2" s="29" t="s">
+      <c r="S2" s="29" t="s">
         <v>455</v>
       </c>
-      <c r="R2" s="29" t="s">
+      <c r="T2" s="29" t="s">
         <v>456</v>
       </c>
-      <c r="S2" s="29" t="s">
+      <c r="U2" s="29" t="s">
         <v>457</v>
       </c>
-      <c r="T2" s="29" t="s">
+      <c r="V2" s="29" t="s">
         <v>458</v>
       </c>
-      <c r="U2" s="29" t="s">
+      <c r="W2" s="29" t="s">
         <v>459</v>
       </c>
-      <c r="V2" s="29" t="s">
+      <c r="X2" s="29" t="s">
         <v>460</v>
       </c>
-      <c r="W2" s="29" t="s">
+      <c r="Y2" s="29" t="s">
         <v>461</v>
       </c>
-      <c r="X2" s="29" t="s">
+      <c r="Z2" s="29" t="s">
         <v>462</v>
       </c>
-      <c r="Y2" s="29" t="s">
+      <c r="AA2" s="29" t="s">
         <v>463</v>
       </c>
-      <c r="Z2" s="29" t="s">
+      <c r="AB2" s="29" t="s">
         <v>464</v>
       </c>
-      <c r="AA2" s="29" t="s">
+      <c r="AC2" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="AB2" s="29" t="s">
+      <c r="AD2" s="31" t="s">
         <v>466</v>
       </c>
-      <c r="AC2" s="31" t="s">
+      <c r="AE2" s="29" t="s">
         <v>467</v>
       </c>
-      <c r="AD2" s="31" t="s">
+      <c r="AF2" s="31" t="s">
         <v>468</v>
       </c>
-      <c r="AE2" s="29" t="s">
+      <c r="AG2" s="29" t="s">
         <v>469</v>
       </c>
-      <c r="AF2" s="31" t="s">
+      <c r="AH2" s="31" t="s">
         <v>470</v>
       </c>
-      <c r="AG2" s="29" t="s">
+      <c r="AI2" s="29" t="s">
         <v>471</v>
       </c>
-      <c r="AH2" s="31" t="s">
+      <c r="AJ2" s="29" t="s">
         <v>472</v>
       </c>
-      <c r="AI2" s="29" t="s">
+      <c r="AK2" s="32" t="s">
         <v>473</v>
       </c>
-      <c r="AJ2" s="29" t="s">
+      <c r="AL2" s="31" t="s">
         <v>474</v>
       </c>
-      <c r="AK2" s="32" t="s">
+      <c r="AM2" s="32" t="s">
         <v>475</v>
       </c>
-      <c r="AL2" s="31" t="s">
+      <c r="AN2" s="29" t="s">
         <v>476</v>
       </c>
-      <c r="AM2" s="32" t="s">
+      <c r="AO2" s="31" t="s">
         <v>477</v>
       </c>
-      <c r="AN2" s="29" t="s">
+      <c r="AP2" s="33" t="s">
         <v>478</v>
       </c>
-      <c r="AO2" s="31" t="s">
+      <c r="AQ2" s="31" t="s">
         <v>479</v>
       </c>
-      <c r="AP2" s="33" t="s">
+      <c r="AR2" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="AQ2" s="31" t="s">
+      <c r="AS2" s="31" t="s">
         <v>481</v>
       </c>
-      <c r="AR2" s="31" t="s">
+      <c r="AT2" s="31" t="s">
         <v>482</v>
       </c>
-      <c r="AS2" s="31" t="s">
+      <c r="AU2" t="s">
         <v>483</v>
       </c>
-      <c r="AT2" s="31" t="s">
+      <c r="AV2" t="s">
         <v>484</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>485</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>486</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:49" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -11023,7 +11080,7 @@
     </row>
     <row r="4" spans="1:49" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B4" s="40">
         <v>1</v>
@@ -11172,7 +11229,7 @@
     </row>
     <row r="5" spans="1:49" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -11321,7 +11378,7 @@
     </row>
     <row r="6" spans="1:49" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -11470,7 +11527,7 @@
     </row>
     <row r="7" spans="1:49" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -11619,7 +11676,7 @@
     </row>
     <row r="8" spans="1:49" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -11768,7 +11825,7 @@
     </row>
     <row r="9" spans="1:49" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -11917,7 +11974,7 @@
     </row>
     <row r="10" spans="1:49" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -12066,7 +12123,7 @@
     </row>
     <row r="11" spans="1:49" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B11" s="40">
         <v>101</v>
@@ -12658,7 +12715,7 @@
         <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
@@ -12666,13 +12723,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
@@ -12680,13 +12737,13 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
@@ -12694,13 +12751,13 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
@@ -12708,7 +12765,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -12722,13 +12779,13 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
@@ -12736,7 +12793,7 @@
         <v>6</v>
       </c>
       <c r="G10" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
@@ -12744,7 +12801,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
@@ -12752,37 +12809,37 @@
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
